--- a/Iteration_1/project_tracker.xlsx
+++ b/Iteration_1/project_tracker.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5320FAAF-258A-4259-B004-449536AC8D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E37017-C8E5-47E6-A310-EB81FA96FED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
@@ -309,9 +309,6 @@
     <t>Tic Tac Toe Handler - structure diagram</t>
   </si>
   <si>
-    <t>Risharbh Agarwal, Richard Nguyen, Mohammad Moustaqim</t>
-  </si>
-  <si>
     <t>Connect 4 Queue - use case diagram</t>
   </si>
   <si>
@@ -319,6 +316,9 @@
   </si>
   <si>
     <t>Game Piece - structure diagram</t>
+  </si>
+  <si>
+    <t>Rishabh Agarwal, Richard Nguyen, Mohammad Moustaqim</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -912,7 +912,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1585,22 +1585,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J563"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="56.36328125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" style="18" customWidth="1"/>
-    <col min="5" max="6" width="16.81640625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="6.71875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="56.38671875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" style="18" customWidth="1"/>
+    <col min="5" max="6" width="16.83203125" style="19" customWidth="1"/>
     <col min="7" max="8" width="16" style="18" customWidth="1"/>
-    <col min="9" max="9" width="85.6328125" style="18" customWidth="1"/>
-    <col min="10" max="10" width="6.7265625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="4.1796875" style="2" customWidth="1"/>
-    <col min="12" max="36" width="3.26953125" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="9.08984375" style="2"/>
+    <col min="9" max="9" width="85.609375" style="18" customWidth="1"/>
+    <col min="10" max="10" width="6.71875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" style="2" customWidth="1"/>
+    <col min="12" max="36" width="3.27734375" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1612,7 +1612,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="25" t="s">
         <v>11</v>
@@ -1630,7 +1630,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1642,7 +1642,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="16" t="s">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="J4" s="10"/>
     </row>
-    <row r="5" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="17" t="s">
         <v>49</v>
@@ -1697,7 +1697,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="17" t="s">
         <v>43</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="17" t="s">
         <v>44</v>
@@ -1753,7 +1753,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="17" t="s">
         <v>45</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>46</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>47</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="17" t="s">
         <v>48</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="17" t="s">
         <v>64</v>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="17" t="s">
         <v>68</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="17" t="s">
         <v>69</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="17" t="s">
         <v>70</v>
       </c>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="I15" s="17"/>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
         <v>71</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
         <v>73</v>
       </c>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I17" s="17"/>
     </row>
-    <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
         <v>74</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="17" t="s">
         <v>75</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="17" t="s">
         <v>77</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="17" t="s">
         <v>78</v>
       </c>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I21" s="17"/>
     </row>
-    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17" t="s">
         <v>79</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="17" t="s">
         <v>80</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
         <v>81</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
         <v>82</v>
       </c>
@@ -2244,10 +2244,10 @@
         <v>4</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="17" t="s">
         <v>83</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
         <v>84</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
         <v>86</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="17" t="s">
         <v>87</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I29" s="17"/>
     </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="17" t="s">
         <v>88</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="17" t="s">
         <v>89</v>
       </c>
@@ -2405,9 +2405,9 @@
       </c>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>15</v>
@@ -2430,9 +2430,9 @@
       </c>
       <c r="I32" s="17"/>
     </row>
-    <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>15</v>
@@ -2455,9 +2455,9 @@
       </c>
       <c r="I33" s="17"/>
     </row>
-    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>15</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I34" s="17"/>
     </row>
-    <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="I35" s="17"/>
     </row>
-    <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I36" s="17"/>
     </row>
-    <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="I37" s="17"/>
     </row>
-    <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="I38" s="17"/>
     </row>
-    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I39" s="17"/>
     </row>
-    <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I40" s="17"/>
     </row>
-    <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I41" s="17"/>
     </row>
-    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="I42" s="17"/>
     </row>
-    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I43" s="17"/>
     </row>
-    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="I44" s="17"/>
     </row>
-    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I45" s="17"/>
     </row>
-    <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="I46" s="17"/>
     </row>
-    <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I47" s="17"/>
     </row>
-    <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I48" s="17"/>
     </row>
-    <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I49" s="17"/>
     </row>
-    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="I50" s="17"/>
     </row>
-    <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="I51" s="17"/>
     </row>
-    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I52" s="17"/>
     </row>
-    <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="I53" s="17"/>
     </row>
-    <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="I54" s="17"/>
     </row>
-    <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I55" s="17"/>
     </row>
-    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="I56" s="17"/>
     </row>
-    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="I57" s="17"/>
     </row>
-    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I58" s="17"/>
     </row>
-    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="I59" s="17"/>
     </row>
-    <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="I60" s="17"/>
     </row>
-    <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I61" s="17"/>
     </row>
-    <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I62" s="17"/>
     </row>
-    <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I63" s="17"/>
     </row>
-    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="I64" s="17"/>
     </row>
-    <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="I65" s="17"/>
     </row>
-    <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="I66" s="17"/>
     </row>
-    <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I67" s="17"/>
     </row>
-    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="I68" s="17"/>
     </row>
-    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="I69" s="17"/>
     </row>
-    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I70" s="17"/>
     </row>
-    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="I71" s="17"/>
     </row>
-    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="I72" s="17"/>
     </row>
-    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I73" s="17"/>
     </row>
-    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="I74" s="17"/>
     </row>
-    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I75" s="17"/>
     </row>
-    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I76" s="17"/>
     </row>
-    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I77" s="17"/>
     </row>
-    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
       <c r="D78" s="17"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I78" s="17"/>
     </row>
-    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="I79" s="17"/>
     </row>
-    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
       <c r="D80" s="17"/>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I80" s="17"/>
     </row>
-    <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I81" s="17"/>
     </row>
-    <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="I82" s="17"/>
     </row>
-    <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="17"/>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="I83" s="17"/>
     </row>
-    <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I84" s="17"/>
     </row>
-    <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
       <c r="D85" s="17"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I85" s="17"/>
     </row>
-    <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
       <c r="D86" s="17"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I86" s="17"/>
     </row>
-    <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="17"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="I87" s="17"/>
     </row>
-    <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="I88" s="17"/>
     </row>
-    <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="17"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I89" s="17"/>
     </row>
-    <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I90" s="17"/>
     </row>
-    <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="I91" s="17"/>
     </row>
-    <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="17"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
       <c r="D93" s="17"/>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I93" s="17"/>
     </row>
-    <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
       <c r="D94" s="17"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I94" s="17"/>
     </row>
-    <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
       <c r="D95" s="17"/>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="I95" s="17"/>
     </row>
-    <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
       <c r="D96" s="17"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="I96" s="17"/>
     </row>
-    <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
       <c r="D97" s="17"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="I97" s="17"/>
     </row>
-    <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
       <c r="D98" s="17"/>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="I98" s="17"/>
     </row>
-    <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B99" s="17"/>
       <c r="C99" s="17"/>
       <c r="D99" s="17"/>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="I99" s="17"/>
     </row>
-    <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
       <c r="D100" s="17"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I100" s="17"/>
     </row>
-    <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
       <c r="D101" s="17"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="I101" s="17"/>
     </row>
-    <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
       <c r="D102" s="17"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I102" s="17"/>
     </row>
-    <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
       <c r="D103" s="17"/>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I103" s="17"/>
     </row>
-    <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="I104" s="17"/>
     </row>
-    <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I105" s="17"/>
     </row>
-    <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="I106" s="17"/>
     </row>
-    <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="I107" s="17"/>
     </row>
-    <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="I108" s="17"/>
     </row>
-    <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="I109" s="17"/>
     </row>
-    <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I110" s="17"/>
     </row>
-    <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I111" s="17"/>
     </row>
-    <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I112" s="17"/>
     </row>
-    <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I113" s="17"/>
     </row>
-    <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="I114" s="17"/>
     </row>
-    <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I115" s="17"/>
     </row>
-    <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I116" s="17"/>
     </row>
-    <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I117" s="17"/>
     </row>
-    <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="I118" s="17"/>
     </row>
-    <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I119" s="17"/>
     </row>
-    <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I120" s="17"/>
     </row>
-    <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I121" s="17"/>
     </row>
-    <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I122" s="17"/>
     </row>
-    <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="I123" s="17"/>
     </row>
-    <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I124" s="17"/>
     </row>
-    <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I125" s="17"/>
     </row>
-    <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="I126" s="17"/>
     </row>
-    <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I127" s="17"/>
     </row>
-    <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
       <c r="D128" s="17"/>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="I128" s="17"/>
     </row>
-    <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I129" s="17"/>
     </row>
-    <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I130" s="17"/>
     </row>
-    <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I131" s="17"/>
     </row>
-    <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="I132" s="17"/>
     </row>
-    <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="I133" s="17"/>
     </row>
-    <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="I134" s="17"/>
     </row>
-    <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I135" s="17"/>
     </row>
-    <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="I136" s="17"/>
     </row>
-    <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I137" s="17"/>
     </row>
-    <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="I138" s="17"/>
     </row>
-    <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I139" s="17"/>
     </row>
-    <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
       <c r="D140" s="17"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I140" s="17"/>
     </row>
-    <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
       <c r="D141" s="17"/>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="I141" s="17"/>
     </row>
-    <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
       <c r="D142" s="17"/>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="I142" s="17"/>
     </row>
-    <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="17"/>
       <c r="C143" s="17"/>
       <c r="D143" s="17"/>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="I143" s="17"/>
     </row>
-    <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
       <c r="D144" s="17"/>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I144" s="17"/>
     </row>
-    <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B145" s="17"/>
       <c r="C145" s="17"/>
       <c r="D145" s="17"/>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I145" s="17"/>
     </row>
-    <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
       <c r="D146" s="17"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I146" s="17"/>
     </row>
-    <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="17"/>
       <c r="C147" s="17"/>
       <c r="D147" s="17"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I147" s="17"/>
     </row>
-    <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
       <c r="D148" s="17"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="I148" s="17"/>
     </row>
-    <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B149" s="17"/>
       <c r="C149" s="17"/>
       <c r="D149" s="17"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I149" s="17"/>
     </row>
-    <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I150" s="17"/>
     </row>
-    <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B151" s="17"/>
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="I151" s="17"/>
     </row>
-    <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="I152" s="17"/>
     </row>
-    <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B153" s="17"/>
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="I153" s="17"/>
     </row>
-    <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="I154" s="17"/>
     </row>
-    <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B155" s="17"/>
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I155" s="17"/>
     </row>
-    <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="I156" s="17"/>
     </row>
-    <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B157" s="17"/>
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="I157" s="17"/>
     </row>
-    <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I158" s="17"/>
     </row>
-    <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B159" s="17"/>
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="I159" s="17"/>
     </row>
-    <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I160" s="17"/>
     </row>
-    <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="17"/>
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="I161" s="17"/>
     </row>
-    <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
       <c r="D162" s="17"/>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="I162" s="17"/>
     </row>
-    <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B163" s="17"/>
       <c r="C163" s="17"/>
       <c r="D163" s="17"/>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="I163" s="17"/>
     </row>
-    <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
       <c r="D164" s="17"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="I164" s="17"/>
     </row>
-    <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B165" s="17"/>
       <c r="C165" s="17"/>
       <c r="D165" s="17"/>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I165" s="17"/>
     </row>
-    <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
       <c r="D166" s="17"/>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="I166" s="17"/>
     </row>
-    <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B167" s="17"/>
       <c r="C167" s="17"/>
       <c r="D167" s="17"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="I167" s="17"/>
     </row>
-    <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
       <c r="D168" s="17"/>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I168" s="17"/>
     </row>
-    <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B169" s="17"/>
       <c r="C169" s="17"/>
       <c r="D169" s="17"/>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I169" s="17"/>
     </row>
-    <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
       <c r="D170" s="17"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I170" s="17"/>
     </row>
-    <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B171" s="17"/>
       <c r="C171" s="17"/>
       <c r="D171" s="17"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I171" s="17"/>
     </row>
-    <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
       <c r="D172" s="17"/>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I172" s="17"/>
     </row>
-    <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B173" s="17"/>
       <c r="C173" s="17"/>
       <c r="D173" s="17"/>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="I173" s="17"/>
     </row>
-    <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
       <c r="D174" s="17"/>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="I174" s="17"/>
     </row>
-    <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B175" s="17"/>
       <c r="C175" s="17"/>
       <c r="D175" s="17"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I175" s="17"/>
     </row>
-    <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
       <c r="D176" s="17"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="I176" s="17"/>
     </row>
-    <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B177" s="17"/>
       <c r="C177" s="17"/>
       <c r="D177" s="17"/>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="I177" s="17"/>
     </row>
-    <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
       <c r="D178" s="17"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="I178" s="17"/>
     </row>
-    <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I179" s="17"/>
     </row>
-    <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
       <c r="D180" s="17"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I180" s="17"/>
     </row>
-    <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
       <c r="D181" s="17"/>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I181" s="17"/>
     </row>
-    <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
       <c r="D182" s="17"/>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="I182" s="17"/>
     </row>
-    <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
       <c r="D183" s="17"/>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I183" s="17"/>
     </row>
-    <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
       <c r="D184" s="17"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="I184" s="17"/>
     </row>
-    <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I185" s="17"/>
     </row>
-    <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
       <c r="D186" s="17"/>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="I186" s="17"/>
     </row>
-    <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
       <c r="D187" s="17"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="I187" s="17"/>
     </row>
-    <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
       <c r="D188" s="17"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="I188" s="17"/>
     </row>
-    <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
       <c r="D189" s="17"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I189" s="17"/>
     </row>
-    <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
       <c r="D190" s="17"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I190" s="17"/>
     </row>
-    <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="I191" s="17"/>
     </row>
-    <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
       <c r="D192" s="17"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I192" s="17"/>
     </row>
-    <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B193" s="17"/>
       <c r="C193" s="17"/>
       <c r="D193" s="17"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I193" s="17"/>
     </row>
-    <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
       <c r="D194" s="17"/>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="I194" s="17"/>
     </row>
-    <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
       <c r="D195" s="17"/>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I195" s="17"/>
     </row>
-    <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="I196" s="17"/>
     </row>
-    <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
       <c r="D197" s="17"/>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I197" s="17"/>
     </row>
-    <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
       <c r="D198" s="17"/>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I198" s="17"/>
     </row>
-    <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B199" s="17"/>
       <c r="C199" s="17"/>
       <c r="D199" s="17"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I199" s="17"/>
     </row>
-    <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
       <c r="D200" s="17"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I200" s="17"/>
     </row>
-    <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
       <c r="D201" s="17"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="I201" s="17"/>
     </row>
-    <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="I202" s="17"/>
     </row>
-    <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B203" s="17"/>
       <c r="C203" s="17"/>
       <c r="D203" s="17"/>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I203" s="17"/>
     </row>
-    <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
       <c r="D204" s="17"/>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="I204" s="17"/>
     </row>
-    <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
       <c r="D205" s="17"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I205" s="17"/>
     </row>
-    <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
       <c r="D206" s="17"/>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="I206" s="17"/>
     </row>
-    <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B207" s="17"/>
       <c r="C207" s="17"/>
       <c r="D207" s="17"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I207" s="17"/>
     </row>
-    <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
       <c r="D208" s="17"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I208" s="17"/>
     </row>
-    <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
       <c r="D209" s="17"/>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="I209" s="17"/>
     </row>
-    <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
       <c r="D210" s="17"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I210" s="17"/>
     </row>
-    <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B211" s="17"/>
       <c r="C211" s="17"/>
       <c r="D211" s="17"/>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I211" s="17"/>
     </row>
-    <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B212" s="17"/>
       <c r="C212" s="17"/>
       <c r="D212" s="17"/>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="I212" s="17"/>
     </row>
-    <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B213" s="17"/>
       <c r="C213" s="17"/>
       <c r="D213" s="17"/>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="I213" s="17"/>
     </row>
-    <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B214" s="17"/>
       <c r="C214" s="17"/>
       <c r="D214" s="17"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="I214" s="17"/>
     </row>
-    <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B215" s="17"/>
       <c r="C215" s="17"/>
       <c r="D215" s="17"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I215" s="17"/>
     </row>
-    <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B216" s="17"/>
       <c r="C216" s="17"/>
       <c r="D216" s="17"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I216" s="17"/>
     </row>
-    <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B217" s="17"/>
       <c r="C217" s="17"/>
       <c r="D217" s="17"/>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I217" s="17"/>
     </row>
-    <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="17"/>
       <c r="C218" s="17"/>
       <c r="D218" s="17"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I218" s="17"/>
     </row>
-    <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B219" s="17"/>
       <c r="C219" s="17"/>
       <c r="D219" s="17"/>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="I219" s="17"/>
     </row>
-    <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
       <c r="D220" s="17"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I220" s="17"/>
     </row>
-    <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B221" s="17"/>
       <c r="C221" s="17"/>
       <c r="D221" s="17"/>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="I221" s="17"/>
     </row>
-    <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
       <c r="D222" s="17"/>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="I222" s="17"/>
     </row>
-    <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B223" s="17"/>
       <c r="C223" s="17"/>
       <c r="D223" s="17"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="I223" s="17"/>
     </row>
-    <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B224" s="17"/>
       <c r="C224" s="17"/>
       <c r="D224" s="17"/>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="I224" s="17"/>
     </row>
-    <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B225" s="17"/>
       <c r="C225" s="17"/>
       <c r="D225" s="17"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I225" s="17"/>
     </row>
-    <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B226" s="17"/>
       <c r="C226" s="17"/>
       <c r="D226" s="17"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I226" s="17"/>
     </row>
-    <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
       <c r="D227" s="17"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I227" s="17"/>
     </row>
-    <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
       <c r="D228" s="17"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="I228" s="17"/>
     </row>
-    <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
       <c r="D229" s="17"/>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="I229" s="17"/>
     </row>
-    <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B230" s="17"/>
       <c r="C230" s="17"/>
       <c r="D230" s="17"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I230" s="17"/>
     </row>
-    <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B231" s="17"/>
       <c r="C231" s="17"/>
       <c r="D231" s="17"/>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I231" s="17"/>
     </row>
-    <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B232" s="17"/>
       <c r="C232" s="17"/>
       <c r="D232" s="17"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="I232" s="17"/>
     </row>
-    <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B233" s="17"/>
       <c r="C233" s="17"/>
       <c r="D233" s="17"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I233" s="17"/>
     </row>
-    <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B234" s="17"/>
       <c r="C234" s="17"/>
       <c r="D234" s="17"/>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I234" s="17"/>
     </row>
-    <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B235" s="17"/>
       <c r="C235" s="17"/>
       <c r="D235" s="17"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I235" s="17"/>
     </row>
-    <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B236" s="17"/>
       <c r="C236" s="17"/>
       <c r="D236" s="17"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I236" s="17"/>
     </row>
-    <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B237" s="17"/>
       <c r="C237" s="17"/>
       <c r="D237" s="17"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I237" s="17"/>
     </row>
-    <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B238" s="17"/>
       <c r="C238" s="17"/>
       <c r="D238" s="17"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="I238" s="17"/>
     </row>
-    <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B239" s="17"/>
       <c r="C239" s="17"/>
       <c r="D239" s="17"/>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I239" s="17"/>
     </row>
-    <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B240" s="17"/>
       <c r="C240" s="17"/>
       <c r="D240" s="17"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I240" s="17"/>
     </row>
-    <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
       <c r="D241" s="17"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I241" s="17"/>
     </row>
-    <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
       <c r="D242" s="17"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="I242" s="17"/>
     </row>
-    <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
       <c r="D243" s="17"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="I243" s="17"/>
     </row>
-    <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
       <c r="D244" s="17"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="I244" s="17"/>
     </row>
-    <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B245" s="17"/>
       <c r="C245" s="17"/>
       <c r="D245" s="17"/>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I245" s="17"/>
     </row>
-    <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
       <c r="D246" s="17"/>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="I246" s="17"/>
     </row>
-    <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B247" s="17"/>
       <c r="C247" s="17"/>
       <c r="D247" s="17"/>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="I247" s="17"/>
     </row>
-    <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
       <c r="D248" s="17"/>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I248" s="17"/>
     </row>
-    <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B249" s="17"/>
       <c r="C249" s="17"/>
       <c r="D249" s="17"/>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="I249" s="17"/>
     </row>
-    <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
       <c r="D250" s="17"/>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I250" s="17"/>
     </row>
-    <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B251" s="17"/>
       <c r="C251" s="17"/>
       <c r="D251" s="17"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I251" s="17"/>
     </row>
-    <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
       <c r="D252" s="17"/>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="I252" s="17"/>
     </row>
-    <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
       <c r="D253" s="17"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="I253" s="17"/>
     </row>
-    <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
       <c r="D254" s="17"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="I254" s="17"/>
     </row>
-    <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B255" s="17"/>
       <c r="C255" s="17"/>
       <c r="D255" s="17"/>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I255" s="17"/>
     </row>
-    <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
       <c r="D256" s="17"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="I256" s="17"/>
     </row>
-    <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B257" s="17"/>
       <c r="C257" s="17"/>
       <c r="D257" s="17"/>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="I257" s="17"/>
     </row>
-    <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
       <c r="D258" s="17"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="I258" s="17"/>
     </row>
-    <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
       <c r="D259" s="17"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="I259" s="17"/>
     </row>
-    <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
       <c r="D260" s="17"/>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I260" s="17"/>
     </row>
-    <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
       <c r="D261" s="17"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="I261" s="17"/>
     </row>
-    <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B262" s="17"/>
       <c r="C262" s="17"/>
       <c r="D262" s="17"/>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="I262" s="17"/>
     </row>
-    <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
       <c r="D263" s="17"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="I263" s="17"/>
     </row>
-    <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
       <c r="D264" s="17"/>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="I264" s="17"/>
     </row>
-    <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B265" s="17"/>
       <c r="C265" s="17"/>
       <c r="D265" s="17"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I265" s="17"/>
     </row>
-    <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
       <c r="D266" s="17"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="I266" s="17"/>
     </row>
-    <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B267" s="17"/>
       <c r="C267" s="17"/>
       <c r="D267" s="17"/>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="I267" s="17"/>
     </row>
-    <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
       <c r="D268" s="17"/>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="I268" s="17"/>
     </row>
-    <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
       <c r="D269" s="17"/>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="I269" s="17"/>
     </row>
-    <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
       <c r="D270" s="17"/>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I270" s="17"/>
     </row>
-    <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
       <c r="D271" s="17"/>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I271" s="17"/>
     </row>
-    <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
       <c r="D272" s="17"/>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="I272" s="17"/>
     </row>
-    <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
       <c r="D273" s="17"/>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="I273" s="17"/>
     </row>
-    <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
       <c r="D274" s="17"/>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="I274" s="17"/>
     </row>
-    <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
       <c r="D275" s="17"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I275" s="17"/>
     </row>
-    <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
       <c r="D276" s="17"/>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="I276" s="17"/>
     </row>
-    <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B277" s="17"/>
       <c r="C277" s="17"/>
       <c r="D277" s="17"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="I277" s="17"/>
     </row>
-    <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
       <c r="D278" s="17"/>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I278" s="17"/>
     </row>
-    <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B279" s="17"/>
       <c r="C279" s="17"/>
       <c r="D279" s="17"/>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="I279" s="17"/>
     </row>
-    <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B280" s="17"/>
       <c r="C280" s="17"/>
       <c r="D280" s="17"/>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I280" s="17"/>
     </row>
-    <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B281" s="17"/>
       <c r="C281" s="17"/>
       <c r="D281" s="17"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I281" s="17"/>
     </row>
-    <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B282" s="17"/>
       <c r="C282" s="17"/>
       <c r="D282" s="17"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="I282" s="17"/>
     </row>
-    <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
       <c r="D283" s="17"/>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="I283" s="17"/>
     </row>
-    <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B284" s="17"/>
       <c r="C284" s="17"/>
       <c r="D284" s="17"/>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="I284" s="17"/>
     </row>
-    <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B285" s="17"/>
       <c r="C285" s="17"/>
       <c r="D285" s="17"/>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I285" s="17"/>
     </row>
-    <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B286" s="17"/>
       <c r="C286" s="17"/>
       <c r="D286" s="17"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I286" s="17"/>
     </row>
-    <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B287" s="17"/>
       <c r="C287" s="17"/>
       <c r="D287" s="17"/>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="I287" s="17"/>
     </row>
-    <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B288" s="17"/>
       <c r="C288" s="17"/>
       <c r="D288" s="17"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="I288" s="17"/>
     </row>
-    <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B289" s="17"/>
       <c r="C289" s="17"/>
       <c r="D289" s="17"/>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="I289" s="17"/>
     </row>
-    <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B290" s="17"/>
       <c r="C290" s="17"/>
       <c r="D290" s="17"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I290" s="17"/>
     </row>
-    <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B291" s="17"/>
       <c r="C291" s="17"/>
       <c r="D291" s="17"/>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="I291" s="17"/>
     </row>
-    <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B292" s="17"/>
       <c r="C292" s="17"/>
       <c r="D292" s="17"/>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="I292" s="17"/>
     </row>
-    <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B293" s="17"/>
       <c r="C293" s="17"/>
       <c r="D293" s="17"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I293" s="17"/>
     </row>
-    <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B294" s="17"/>
       <c r="C294" s="17"/>
       <c r="D294" s="17"/>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="I294" s="17"/>
     </row>
-    <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B295" s="17"/>
       <c r="C295" s="17"/>
       <c r="D295" s="17"/>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I295" s="17"/>
     </row>
-    <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B296" s="17"/>
       <c r="C296" s="17"/>
       <c r="D296" s="17"/>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="I296" s="17"/>
     </row>
-    <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B297" s="17"/>
       <c r="C297" s="17"/>
       <c r="D297" s="17"/>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="I297" s="17"/>
     </row>
-    <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B298" s="17"/>
       <c r="C298" s="17"/>
       <c r="D298" s="17"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="I298" s="17"/>
     </row>
-    <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B299" s="17"/>
       <c r="C299" s="17"/>
       <c r="D299" s="17"/>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="I299" s="17"/>
     </row>
-    <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
       <c r="D300" s="17"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I300" s="17"/>
     </row>
-    <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
       <c r="D301" s="17"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I301" s="17"/>
     </row>
-    <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B302" s="17"/>
       <c r="C302" s="17"/>
       <c r="D302" s="17"/>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="I302" s="17"/>
     </row>
-    <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B303" s="17"/>
       <c r="C303" s="17"/>
       <c r="D303" s="17"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="I303" s="17"/>
     </row>
-    <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B304" s="17"/>
       <c r="C304" s="17"/>
       <c r="D304" s="17"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="I304" s="17"/>
     </row>
-    <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B305" s="17"/>
       <c r="C305" s="17"/>
       <c r="D305" s="17"/>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I305" s="17"/>
     </row>
-    <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
       <c r="D306" s="17"/>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="I306" s="17"/>
     </row>
-    <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
       <c r="D307" s="17"/>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="I307" s="17"/>
     </row>
-    <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
       <c r="D308" s="17"/>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="I308" s="17"/>
     </row>
-    <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
       <c r="D309" s="17"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="I309" s="17"/>
     </row>
-    <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
       <c r="D310" s="17"/>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I310" s="17"/>
     </row>
-    <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B311" s="17"/>
       <c r="C311" s="17"/>
       <c r="D311" s="17"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="I311" s="17"/>
     </row>
-    <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B312" s="17"/>
       <c r="C312" s="17"/>
       <c r="D312" s="17"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="I312" s="17"/>
     </row>
-    <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
       <c r="D313" s="17"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I313" s="17"/>
     </row>
-    <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
       <c r="D314" s="17"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="I314" s="17"/>
     </row>
-    <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B315" s="17"/>
       <c r="C315" s="17"/>
       <c r="D315" s="17"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I315" s="17"/>
     </row>
-    <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B316" s="17"/>
       <c r="C316" s="17"/>
       <c r="D316" s="17"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="I316" s="17"/>
     </row>
-    <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B317" s="17"/>
       <c r="C317" s="17"/>
       <c r="D317" s="17"/>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="I317" s="17"/>
     </row>
-    <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>
       <c r="D318" s="17"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="I318" s="17"/>
     </row>
-    <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B319" s="17"/>
       <c r="C319" s="17"/>
       <c r="D319" s="17"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="I319" s="17"/>
     </row>
-    <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B320" s="17"/>
       <c r="C320" s="17"/>
       <c r="D320" s="17"/>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I320" s="17"/>
     </row>
-    <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B321" s="17"/>
       <c r="C321" s="17"/>
       <c r="D321" s="17"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I321" s="17"/>
     </row>
-    <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B322" s="17"/>
       <c r="C322" s="17"/>
       <c r="D322" s="17"/>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="I322" s="17"/>
     </row>
-    <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B323" s="17"/>
       <c r="C323" s="17"/>
       <c r="D323" s="17"/>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="I323" s="17"/>
     </row>
-    <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B324" s="17"/>
       <c r="C324" s="17"/>
       <c r="D324" s="17"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="I324" s="17"/>
     </row>
-    <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
       <c r="D325" s="17"/>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I325" s="17"/>
     </row>
-    <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B326" s="17"/>
       <c r="C326" s="17"/>
       <c r="D326" s="17"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="I326" s="17"/>
     </row>
-    <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B327" s="17"/>
       <c r="C327" s="17"/>
       <c r="D327" s="17"/>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="I327" s="17"/>
     </row>
-    <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B328" s="17"/>
       <c r="C328" s="17"/>
       <c r="D328" s="17"/>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="I328" s="17"/>
     </row>
-    <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B329" s="17"/>
       <c r="C329" s="17"/>
       <c r="D329" s="17"/>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I329" s="17"/>
     </row>
-    <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B330" s="17"/>
       <c r="C330" s="17"/>
       <c r="D330" s="17"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="I330" s="17"/>
     </row>
-    <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B331" s="17"/>
       <c r="C331" s="17"/>
       <c r="D331" s="17"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I331" s="17"/>
     </row>
-    <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B332" s="17"/>
       <c r="C332" s="17"/>
       <c r="D332" s="17"/>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="I332" s="17"/>
     </row>
-    <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B333" s="17"/>
       <c r="C333" s="17"/>
       <c r="D333" s="17"/>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="I333" s="17"/>
     </row>
-    <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B334" s="17"/>
       <c r="C334" s="17"/>
       <c r="D334" s="17"/>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="I334" s="17"/>
     </row>
-    <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B335" s="17"/>
       <c r="C335" s="17"/>
       <c r="D335" s="17"/>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I335" s="17"/>
     </row>
-    <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B336" s="17"/>
       <c r="C336" s="17"/>
       <c r="D336" s="17"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="I336" s="17"/>
     </row>
-    <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B337" s="17"/>
       <c r="C337" s="17"/>
       <c r="D337" s="17"/>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="I337" s="17"/>
     </row>
-    <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B338" s="17"/>
       <c r="C338" s="17"/>
       <c r="D338" s="17"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I338" s="17"/>
     </row>
-    <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B339" s="17"/>
       <c r="C339" s="17"/>
       <c r="D339" s="17"/>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I339" s="17"/>
     </row>
-    <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B340" s="17"/>
       <c r="C340" s="17"/>
       <c r="D340" s="17"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I340" s="17"/>
     </row>
-    <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B341" s="17"/>
       <c r="C341" s="17"/>
       <c r="D341" s="17"/>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I341" s="17"/>
     </row>
-    <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B342" s="17"/>
       <c r="C342" s="17"/>
       <c r="D342" s="17"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="I342" s="17"/>
     </row>
-    <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B343" s="17"/>
       <c r="C343" s="17"/>
       <c r="D343" s="17"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="I343" s="17"/>
     </row>
-    <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B344" s="17"/>
       <c r="C344" s="17"/>
       <c r="D344" s="17"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="I344" s="17"/>
     </row>
-    <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B345" s="17"/>
       <c r="C345" s="17"/>
       <c r="D345" s="17"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I345" s="17"/>
     </row>
-    <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B346" s="17"/>
       <c r="C346" s="17"/>
       <c r="D346" s="17"/>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="I346" s="17"/>
     </row>
-    <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B347" s="17"/>
       <c r="C347" s="17"/>
       <c r="D347" s="17"/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I347" s="17"/>
     </row>
-    <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B348" s="17"/>
       <c r="C348" s="17"/>
       <c r="D348" s="17"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I348" s="17"/>
     </row>
-    <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B349" s="17"/>
       <c r="C349" s="17"/>
       <c r="D349" s="17"/>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="I349" s="17"/>
     </row>
-    <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B350" s="17"/>
       <c r="C350" s="17"/>
       <c r="D350" s="17"/>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I350" s="17"/>
     </row>
-    <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B351" s="17"/>
       <c r="C351" s="17"/>
       <c r="D351" s="17"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="I351" s="17"/>
     </row>
-    <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B352" s="17"/>
       <c r="C352" s="17"/>
       <c r="D352" s="17"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="I352" s="17"/>
     </row>
-    <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B353" s="17"/>
       <c r="C353" s="17"/>
       <c r="D353" s="17"/>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="I353" s="17"/>
     </row>
-    <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B354" s="17"/>
       <c r="C354" s="17"/>
       <c r="D354" s="17"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="I354" s="17"/>
     </row>
-    <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B355" s="17"/>
       <c r="C355" s="17"/>
       <c r="D355" s="17"/>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I355" s="17"/>
     </row>
-    <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B356" s="17"/>
       <c r="C356" s="17"/>
       <c r="D356" s="17"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="I356" s="17"/>
     </row>
-    <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B357" s="17"/>
       <c r="C357" s="17"/>
       <c r="D357" s="17"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I357" s="17"/>
     </row>
-    <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B358" s="17"/>
       <c r="C358" s="17"/>
       <c r="D358" s="17"/>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I358" s="17"/>
     </row>
-    <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B359" s="17"/>
       <c r="C359" s="17"/>
       <c r="D359" s="17"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="I359" s="17"/>
     </row>
-    <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B360" s="17"/>
       <c r="C360" s="17"/>
       <c r="D360" s="17"/>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="I360" s="17"/>
     </row>
-    <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B361" s="17"/>
       <c r="C361" s="17"/>
       <c r="D361" s="17"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I361" s="17"/>
     </row>
-    <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B362" s="17"/>
       <c r="C362" s="17"/>
       <c r="D362" s="17"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="I362" s="17"/>
     </row>
-    <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B363" s="17"/>
       <c r="C363" s="17"/>
       <c r="D363" s="17"/>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="I363" s="17"/>
     </row>
-    <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B364" s="17"/>
       <c r="C364" s="17"/>
       <c r="D364" s="17"/>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="I364" s="17"/>
     </row>
-    <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B365" s="17"/>
       <c r="C365" s="17"/>
       <c r="D365" s="17"/>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I365" s="17"/>
     </row>
-    <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B366" s="17"/>
       <c r="C366" s="17"/>
       <c r="D366" s="17"/>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="I366" s="17"/>
     </row>
-    <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B367" s="17"/>
       <c r="C367" s="17"/>
       <c r="D367" s="17"/>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="I367" s="17"/>
     </row>
-    <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B368" s="17"/>
       <c r="C368" s="17"/>
       <c r="D368" s="17"/>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="I368" s="17"/>
     </row>
-    <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B369" s="17"/>
       <c r="C369" s="17"/>
       <c r="D369" s="17"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="I369" s="17"/>
     </row>
-    <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B370" s="17"/>
       <c r="C370" s="17"/>
       <c r="D370" s="17"/>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="I370" s="17"/>
     </row>
-    <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B371" s="17"/>
       <c r="C371" s="17"/>
       <c r="D371" s="17"/>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="I371" s="17"/>
     </row>
-    <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B372" s="17"/>
       <c r="C372" s="17"/>
       <c r="D372" s="17"/>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="I372" s="17"/>
     </row>
-    <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B373" s="17"/>
       <c r="C373" s="17"/>
       <c r="D373" s="17"/>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="I373" s="17"/>
     </row>
-    <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B374" s="17"/>
       <c r="C374" s="17"/>
       <c r="D374" s="17"/>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="I374" s="17"/>
     </row>
-    <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B375" s="17"/>
       <c r="C375" s="17"/>
       <c r="D375" s="17"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="I375" s="17"/>
     </row>
-    <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B376" s="17"/>
       <c r="C376" s="17"/>
       <c r="D376" s="17"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="I376" s="17"/>
     </row>
-    <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B377" s="17"/>
       <c r="C377" s="17"/>
       <c r="D377" s="17"/>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="I377" s="17"/>
     </row>
-    <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B378" s="17"/>
       <c r="C378" s="17"/>
       <c r="D378" s="17"/>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="I378" s="17"/>
     </row>
-    <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B379" s="17"/>
       <c r="C379" s="17"/>
       <c r="D379" s="17"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="I379" s="17"/>
     </row>
-    <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B380" s="17"/>
       <c r="C380" s="17"/>
       <c r="D380" s="17"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="I380" s="17"/>
     </row>
-    <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B381" s="17"/>
       <c r="C381" s="17"/>
       <c r="D381" s="17"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I381" s="17"/>
     </row>
-    <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B382" s="17"/>
       <c r="C382" s="17"/>
       <c r="D382" s="17"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="I382" s="17"/>
     </row>
-    <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B383" s="17"/>
       <c r="C383" s="17"/>
       <c r="D383" s="17"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I383" s="17"/>
     </row>
-    <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B384" s="17"/>
       <c r="C384" s="17"/>
       <c r="D384" s="17"/>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I384" s="17"/>
     </row>
-    <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B385" s="17"/>
       <c r="C385" s="17"/>
       <c r="D385" s="17"/>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="I385" s="17"/>
     </row>
-    <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B386" s="17"/>
       <c r="C386" s="17"/>
       <c r="D386" s="17"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="I386" s="17"/>
     </row>
-    <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B387" s="17"/>
       <c r="C387" s="17"/>
       <c r="D387" s="17"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="I387" s="17"/>
     </row>
-    <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B388" s="17"/>
       <c r="C388" s="17"/>
       <c r="D388" s="17"/>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="I388" s="17"/>
     </row>
-    <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B389" s="17"/>
       <c r="C389" s="17"/>
       <c r="D389" s="17"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="I389" s="17"/>
     </row>
-    <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B390" s="17"/>
       <c r="C390" s="17"/>
       <c r="D390" s="17"/>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="I390" s="17"/>
     </row>
-    <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B391" s="17"/>
       <c r="C391" s="17"/>
       <c r="D391" s="17"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I391" s="17"/>
     </row>
-    <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B392" s="17"/>
       <c r="C392" s="17"/>
       <c r="D392" s="17"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="I392" s="17"/>
     </row>
-    <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B393" s="17"/>
       <c r="C393" s="17"/>
       <c r="D393" s="17"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="I393" s="17"/>
     </row>
-    <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B394" s="17"/>
       <c r="C394" s="17"/>
       <c r="D394" s="17"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="I394" s="17"/>
     </row>
-    <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B395" s="17"/>
       <c r="C395" s="17"/>
       <c r="D395" s="17"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="I395" s="17"/>
     </row>
-    <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B396" s="17"/>
       <c r="C396" s="17"/>
       <c r="D396" s="17"/>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="I396" s="17"/>
     </row>
-    <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B397" s="17"/>
       <c r="C397" s="17"/>
       <c r="D397" s="17"/>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="I397" s="17"/>
     </row>
-    <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B398" s="17"/>
       <c r="C398" s="17"/>
       <c r="D398" s="17"/>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="I398" s="17"/>
     </row>
-    <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B399" s="17"/>
       <c r="C399" s="17"/>
       <c r="D399" s="17"/>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="I399" s="17"/>
     </row>
-    <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B400" s="17"/>
       <c r="C400" s="17"/>
       <c r="D400" s="17"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I400" s="17"/>
     </row>
-    <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B401" s="17"/>
       <c r="C401" s="17"/>
       <c r="D401" s="17"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="I401" s="17"/>
     </row>
-    <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B402" s="17"/>
       <c r="C402" s="17"/>
       <c r="D402" s="17"/>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="I402" s="17"/>
     </row>
-    <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B403" s="17"/>
       <c r="C403" s="17"/>
       <c r="D403" s="17"/>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I403" s="17"/>
     </row>
-    <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B404" s="17"/>
       <c r="C404" s="17"/>
       <c r="D404" s="17"/>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="I404" s="17"/>
     </row>
-    <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B405" s="17"/>
       <c r="C405" s="17"/>
       <c r="D405" s="17"/>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="I405" s="17"/>
     </row>
-    <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B406" s="17"/>
       <c r="C406" s="17"/>
       <c r="D406" s="17"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I406" s="17"/>
     </row>
-    <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B407" s="17"/>
       <c r="C407" s="17"/>
       <c r="D407" s="17"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="I407" s="17"/>
     </row>
-    <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B408" s="17"/>
       <c r="C408" s="17"/>
       <c r="D408" s="17"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="I408" s="17"/>
     </row>
-    <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B409" s="17"/>
       <c r="C409" s="17"/>
       <c r="D409" s="17"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="I409" s="17"/>
     </row>
-    <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B410" s="17"/>
       <c r="C410" s="17"/>
       <c r="D410" s="17"/>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="I410" s="17"/>
     </row>
-    <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B411" s="17"/>
       <c r="C411" s="17"/>
       <c r="D411" s="17"/>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="I411" s="17"/>
     </row>
-    <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B412" s="17"/>
       <c r="C412" s="17"/>
       <c r="D412" s="17"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I412" s="17"/>
     </row>
-    <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B413" s="17"/>
       <c r="C413" s="17"/>
       <c r="D413" s="17"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="I413" s="17"/>
     </row>
-    <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B414" s="17"/>
       <c r="C414" s="17"/>
       <c r="D414" s="17"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="I414" s="17"/>
     </row>
-    <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B415" s="17"/>
       <c r="C415" s="17"/>
       <c r="D415" s="17"/>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I415" s="17"/>
     </row>
-    <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B416" s="17"/>
       <c r="C416" s="17"/>
       <c r="D416" s="17"/>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="I416" s="17"/>
     </row>
-    <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B417" s="17"/>
       <c r="C417" s="17"/>
       <c r="D417" s="17"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="I417" s="17"/>
     </row>
-    <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B418" s="17"/>
       <c r="C418" s="17"/>
       <c r="D418" s="17"/>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I418" s="17"/>
     </row>
-    <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B419" s="17"/>
       <c r="C419" s="17"/>
       <c r="D419" s="17"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="I419" s="17"/>
     </row>
-    <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B420" s="17"/>
       <c r="C420" s="17"/>
       <c r="D420" s="17"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="I420" s="17"/>
     </row>
-    <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B421" s="17"/>
       <c r="C421" s="17"/>
       <c r="D421" s="17"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="I421" s="17"/>
     </row>
-    <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B422" s="17"/>
       <c r="C422" s="17"/>
       <c r="D422" s="17"/>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I422" s="17"/>
     </row>
-    <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B423" s="17"/>
       <c r="C423" s="17"/>
       <c r="D423" s="17"/>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="I423" s="17"/>
     </row>
-    <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B424" s="17"/>
       <c r="C424" s="17"/>
       <c r="D424" s="17"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="I424" s="17"/>
     </row>
-    <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B425" s="17"/>
       <c r="C425" s="17"/>
       <c r="D425" s="17"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="I425" s="17"/>
     </row>
-    <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B426" s="17"/>
       <c r="C426" s="17"/>
       <c r="D426" s="17"/>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I426" s="17"/>
     </row>
-    <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B427" s="17"/>
       <c r="C427" s="17"/>
       <c r="D427" s="17"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="I427" s="17"/>
     </row>
-    <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B428" s="17"/>
       <c r="C428" s="17"/>
       <c r="D428" s="17"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="I428" s="17"/>
     </row>
-    <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B429" s="17"/>
       <c r="C429" s="17"/>
       <c r="D429" s="17"/>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="I429" s="17"/>
     </row>
-    <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B430" s="17"/>
       <c r="C430" s="17"/>
       <c r="D430" s="17"/>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="I430" s="17"/>
     </row>
-    <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B431" s="17"/>
       <c r="C431" s="17"/>
       <c r="D431" s="17"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="I431" s="17"/>
     </row>
-    <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B432" s="17"/>
       <c r="C432" s="17"/>
       <c r="D432" s="17"/>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="I432" s="17"/>
     </row>
-    <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B433" s="17"/>
       <c r="C433" s="17"/>
       <c r="D433" s="17"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="I433" s="17"/>
     </row>
-    <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B434" s="17"/>
       <c r="C434" s="17"/>
       <c r="D434" s="17"/>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I434" s="17"/>
     </row>
-    <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B435" s="17"/>
       <c r="C435" s="17"/>
       <c r="D435" s="17"/>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="I435" s="17"/>
     </row>
-    <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B436" s="17"/>
       <c r="C436" s="17"/>
       <c r="D436" s="17"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I436" s="17"/>
     </row>
-    <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B437" s="17"/>
       <c r="C437" s="17"/>
       <c r="D437" s="17"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="I437" s="17"/>
     </row>
-    <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B438" s="17"/>
       <c r="C438" s="17"/>
       <c r="D438" s="17"/>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="I438" s="17"/>
     </row>
-    <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B439" s="17"/>
       <c r="C439" s="17"/>
       <c r="D439" s="17"/>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="I439" s="17"/>
     </row>
-    <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B440" s="17"/>
       <c r="C440" s="17"/>
       <c r="D440" s="17"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="I440" s="17"/>
     </row>
-    <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B441" s="17"/>
       <c r="C441" s="17"/>
       <c r="D441" s="17"/>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I441" s="17"/>
     </row>
-    <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B442" s="17"/>
       <c r="C442" s="17"/>
       <c r="D442" s="17"/>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="I442" s="17"/>
     </row>
-    <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B443" s="17"/>
       <c r="C443" s="17"/>
       <c r="D443" s="17"/>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="I443" s="17"/>
     </row>
-    <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B444" s="17"/>
       <c r="C444" s="17"/>
       <c r="D444" s="17"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="I444" s="17"/>
     </row>
-    <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B445" s="17"/>
       <c r="C445" s="17"/>
       <c r="D445" s="17"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="I445" s="17"/>
     </row>
-    <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B446" s="17"/>
       <c r="C446" s="17"/>
       <c r="D446" s="17"/>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I446" s="17"/>
     </row>
-    <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B447" s="17"/>
       <c r="C447" s="17"/>
       <c r="D447" s="17"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="I447" s="17"/>
     </row>
-    <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B448" s="17"/>
       <c r="C448" s="17"/>
       <c r="D448" s="17"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="I448" s="17"/>
     </row>
-    <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B449" s="17"/>
       <c r="C449" s="17"/>
       <c r="D449" s="17"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="I449" s="17"/>
     </row>
-    <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B450" s="17"/>
       <c r="C450" s="17"/>
       <c r="D450" s="17"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="I450" s="17"/>
     </row>
-    <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B451" s="17"/>
       <c r="C451" s="17"/>
       <c r="D451" s="17"/>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="I451" s="17"/>
     </row>
-    <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B452" s="17"/>
       <c r="C452" s="17"/>
       <c r="D452" s="17"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I452" s="17"/>
     </row>
-    <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B453" s="17"/>
       <c r="C453" s="17"/>
       <c r="D453" s="17"/>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="I453" s="17"/>
     </row>
-    <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B454" s="17"/>
       <c r="C454" s="17"/>
       <c r="D454" s="17"/>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="I454" s="17"/>
     </row>
-    <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B455" s="17"/>
       <c r="C455" s="17"/>
       <c r="D455" s="17"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="I455" s="17"/>
     </row>
-    <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B456" s="17"/>
       <c r="C456" s="17"/>
       <c r="D456" s="17"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I456" s="17"/>
     </row>
-    <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B457" s="17"/>
       <c r="C457" s="17"/>
       <c r="D457" s="17"/>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="I457" s="17"/>
     </row>
-    <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B458" s="17"/>
       <c r="C458" s="17"/>
       <c r="D458" s="17"/>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="I458" s="17"/>
     </row>
-    <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B459" s="17"/>
       <c r="C459" s="17"/>
       <c r="D459" s="17"/>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="I459" s="17"/>
     </row>
-    <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B460" s="17"/>
       <c r="C460" s="17"/>
       <c r="D460" s="17"/>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="I460" s="17"/>
     </row>
-    <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B461" s="17"/>
       <c r="C461" s="17"/>
       <c r="D461" s="17"/>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="I461" s="17"/>
     </row>
-    <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B462" s="17"/>
       <c r="C462" s="17"/>
       <c r="D462" s="17"/>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="I462" s="17"/>
     </row>
-    <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B463" s="17"/>
       <c r="C463" s="17"/>
       <c r="D463" s="17"/>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="I463" s="17"/>
     </row>
-    <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B464" s="17"/>
       <c r="C464" s="17"/>
       <c r="D464" s="17"/>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="I464" s="17"/>
     </row>
-    <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B465" s="17"/>
       <c r="C465" s="17"/>
       <c r="D465" s="17"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I465" s="17"/>
     </row>
-    <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B466" s="17"/>
       <c r="C466" s="17"/>
       <c r="D466" s="17"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="I466" s="17"/>
     </row>
-    <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B467" s="17"/>
       <c r="C467" s="17"/>
       <c r="D467" s="17"/>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I467" s="17"/>
     </row>
-    <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B468" s="17"/>
       <c r="C468" s="17"/>
       <c r="D468" s="17"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="I468" s="17"/>
     </row>
-    <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B469" s="17"/>
       <c r="C469" s="17"/>
       <c r="D469" s="17"/>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="I469" s="17"/>
     </row>
-    <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B470" s="17"/>
       <c r="C470" s="17"/>
       <c r="D470" s="17"/>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I470" s="17"/>
     </row>
-    <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B471" s="17"/>
       <c r="C471" s="17"/>
       <c r="D471" s="17"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="I471" s="17"/>
     </row>
-    <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B472" s="17"/>
       <c r="C472" s="17"/>
       <c r="D472" s="17"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I472" s="17"/>
     </row>
-    <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B473" s="17"/>
       <c r="C473" s="17"/>
       <c r="D473" s="17"/>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="I473" s="17"/>
     </row>
-    <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B474" s="17"/>
       <c r="C474" s="17"/>
       <c r="D474" s="17"/>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="I474" s="17"/>
     </row>
-    <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B475" s="17"/>
       <c r="C475" s="17"/>
       <c r="D475" s="17"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="I475" s="17"/>
     </row>
-    <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B476" s="17"/>
       <c r="C476" s="17"/>
       <c r="D476" s="17"/>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="I476" s="17"/>
     </row>
-    <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B477" s="17"/>
       <c r="C477" s="17"/>
       <c r="D477" s="17"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="I477" s="17"/>
     </row>
-    <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B478" s="17"/>
       <c r="C478" s="17"/>
       <c r="D478" s="17"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="I478" s="17"/>
     </row>
-    <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B479" s="17"/>
       <c r="C479" s="17"/>
       <c r="D479" s="17"/>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="I479" s="17"/>
     </row>
-    <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B480" s="17"/>
       <c r="C480" s="17"/>
       <c r="D480" s="17"/>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="I480" s="17"/>
     </row>
-    <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B481" s="17"/>
       <c r="C481" s="17"/>
       <c r="D481" s="17"/>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I481" s="17"/>
     </row>
-    <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B482" s="17"/>
       <c r="C482" s="17"/>
       <c r="D482" s="17"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="I482" s="17"/>
     </row>
-    <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B483" s="17"/>
       <c r="C483" s="17"/>
       <c r="D483" s="17"/>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="I483" s="17"/>
     </row>
-    <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B484" s="17"/>
       <c r="C484" s="17"/>
       <c r="D484" s="17"/>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="I484" s="17"/>
     </row>
-    <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B485" s="17"/>
       <c r="C485" s="17"/>
       <c r="D485" s="17"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I485" s="17"/>
     </row>
-    <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B486" s="17"/>
       <c r="C486" s="17"/>
       <c r="D486" s="17"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="I486" s="17"/>
     </row>
-    <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B487" s="17"/>
       <c r="C487" s="17"/>
       <c r="D487" s="17"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="I487" s="17"/>
     </row>
-    <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B488" s="17"/>
       <c r="C488" s="17"/>
       <c r="D488" s="17"/>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="I488" s="17"/>
     </row>
-    <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B489" s="17"/>
       <c r="C489" s="17"/>
       <c r="D489" s="17"/>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I489" s="17"/>
     </row>
-    <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B490" s="17"/>
       <c r="C490" s="17"/>
       <c r="D490" s="17"/>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="I490" s="17"/>
     </row>
-    <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B491" s="17"/>
       <c r="C491" s="17"/>
       <c r="D491" s="17"/>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="I491" s="17"/>
     </row>
-    <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B492" s="17"/>
       <c r="C492" s="17"/>
       <c r="D492" s="17"/>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="I492" s="17"/>
     </row>
-    <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B493" s="17"/>
       <c r="C493" s="17"/>
       <c r="D493" s="17"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="I493" s="17"/>
     </row>
-    <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B494" s="17"/>
       <c r="C494" s="17"/>
       <c r="D494" s="17"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="I494" s="17"/>
     </row>
-    <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B495" s="17"/>
       <c r="C495" s="17"/>
       <c r="D495" s="17"/>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="I495" s="17"/>
     </row>
-    <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B496" s="17"/>
       <c r="C496" s="17"/>
       <c r="D496" s="17"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I496" s="17"/>
     </row>
-    <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B497" s="17"/>
       <c r="C497" s="17"/>
       <c r="D497" s="17"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I497" s="17"/>
     </row>
-    <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B498" s="17"/>
       <c r="C498" s="17"/>
       <c r="D498" s="17"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="I498" s="17"/>
     </row>
-    <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B499" s="17"/>
       <c r="C499" s="17"/>
       <c r="D499" s="17"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="I499" s="17"/>
     </row>
-    <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B500" s="17"/>
       <c r="C500" s="17"/>
       <c r="D500" s="17"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="I500" s="17"/>
     </row>
-    <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B501" s="17"/>
       <c r="C501" s="17"/>
       <c r="D501" s="17"/>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="I501" s="17"/>
     </row>
-    <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B502" s="17"/>
       <c r="C502" s="17"/>
       <c r="D502" s="17"/>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="I502" s="17"/>
     </row>
-    <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B503" s="17"/>
       <c r="C503" s="17"/>
       <c r="D503" s="17"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="I503" s="17"/>
     </row>
-    <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B504" s="17"/>
       <c r="C504" s="17"/>
       <c r="D504" s="17"/>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="I504" s="17"/>
     </row>
-    <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B505" s="17"/>
       <c r="C505" s="17"/>
       <c r="D505" s="17"/>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="I505" s="17"/>
     </row>
-    <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B506" s="17"/>
       <c r="C506" s="17"/>
       <c r="D506" s="17"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="I506" s="17"/>
     </row>
-    <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B507" s="17"/>
       <c r="C507" s="17"/>
       <c r="D507" s="17"/>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="I507" s="17"/>
     </row>
-    <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B508" s="17"/>
       <c r="C508" s="17"/>
       <c r="D508" s="17"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="I508" s="17"/>
     </row>
-    <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B509" s="17"/>
       <c r="C509" s="17"/>
       <c r="D509" s="17"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="I509" s="17"/>
     </row>
-    <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B510" s="17"/>
       <c r="C510" s="17"/>
       <c r="D510" s="17"/>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="I510" s="17"/>
     </row>
-    <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B511" s="17"/>
       <c r="C511" s="17"/>
       <c r="D511" s="17"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="I511" s="17"/>
     </row>
-    <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B512" s="17"/>
       <c r="C512" s="17"/>
       <c r="D512" s="17"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I512" s="17"/>
     </row>
-    <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B513" s="17"/>
       <c r="C513" s="17"/>
       <c r="D513" s="17"/>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I513" s="17"/>
     </row>
-    <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B514" s="17"/>
       <c r="C514" s="17"/>
       <c r="D514" s="17"/>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="I514" s="17"/>
     </row>
-    <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B515" s="17"/>
       <c r="C515" s="17"/>
       <c r="D515" s="17"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="I515" s="17"/>
     </row>
-    <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B516" s="17"/>
       <c r="C516" s="17"/>
       <c r="D516" s="17"/>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="I516" s="17"/>
     </row>
-    <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B517" s="17"/>
       <c r="C517" s="17"/>
       <c r="D517" s="17"/>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="I517" s="17"/>
     </row>
-    <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B518" s="17"/>
       <c r="C518" s="17"/>
       <c r="D518" s="17"/>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="I518" s="17"/>
     </row>
-    <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B519" s="17"/>
       <c r="C519" s="17"/>
       <c r="D519" s="17"/>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="I519" s="17"/>
     </row>
-    <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B520" s="17"/>
       <c r="C520" s="17"/>
       <c r="D520" s="17"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="I520" s="17"/>
     </row>
-    <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B521" s="17"/>
       <c r="C521" s="17"/>
       <c r="D521" s="17"/>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="I521" s="17"/>
     </row>
-    <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B522" s="17"/>
       <c r="C522" s="17"/>
       <c r="D522" s="17"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="I522" s="17"/>
     </row>
-    <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B523" s="17"/>
       <c r="C523" s="17"/>
       <c r="D523" s="17"/>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="I523" s="17"/>
     </row>
-    <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B524" s="17"/>
       <c r="C524" s="17"/>
       <c r="D524" s="17"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="I524" s="17"/>
     </row>
-    <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B525" s="17"/>
       <c r="C525" s="17"/>
       <c r="D525" s="17"/>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="I525" s="17"/>
     </row>
-    <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B526" s="17"/>
       <c r="C526" s="17"/>
       <c r="D526" s="17"/>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="I526" s="17"/>
     </row>
-    <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B527" s="17"/>
       <c r="C527" s="17"/>
       <c r="D527" s="17"/>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="I527" s="17"/>
     </row>
-    <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B528" s="17"/>
       <c r="C528" s="17"/>
       <c r="D528" s="17"/>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I528" s="17"/>
     </row>
-    <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B529" s="17"/>
       <c r="C529" s="17"/>
       <c r="D529" s="17"/>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="I529" s="17"/>
     </row>
-    <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B530" s="17"/>
       <c r="C530" s="17"/>
       <c r="D530" s="17"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="I530" s="17"/>
     </row>
-    <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B531" s="17"/>
       <c r="C531" s="17"/>
       <c r="D531" s="17"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I531" s="17"/>
     </row>
-    <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B532" s="17"/>
       <c r="C532" s="17"/>
       <c r="D532" s="17"/>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="I532" s="17"/>
     </row>
-    <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B533" s="17"/>
       <c r="C533" s="17"/>
       <c r="D533" s="17"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I533" s="17"/>
     </row>
-    <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B534" s="17"/>
       <c r="C534" s="17"/>
       <c r="D534" s="17"/>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="I534" s="17"/>
     </row>
-    <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B535" s="17"/>
       <c r="C535" s="17"/>
       <c r="D535" s="17"/>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I535" s="17"/>
     </row>
-    <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B536" s="17"/>
       <c r="C536" s="17"/>
       <c r="D536" s="17"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="I536" s="17"/>
     </row>
-    <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B537" s="17"/>
       <c r="C537" s="17"/>
       <c r="D537" s="17"/>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I537" s="17"/>
     </row>
-    <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B538" s="17"/>
       <c r="C538" s="17"/>
       <c r="D538" s="17"/>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="I538" s="17"/>
     </row>
-    <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B539" s="17"/>
       <c r="C539" s="17"/>
       <c r="D539" s="17"/>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="I539" s="17"/>
     </row>
-    <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B540" s="17"/>
       <c r="C540" s="17"/>
       <c r="D540" s="17"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I540" s="17"/>
     </row>
-    <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B541" s="17"/>
       <c r="C541" s="17"/>
       <c r="D541" s="17"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="I541" s="17"/>
     </row>
-    <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B542" s="17"/>
       <c r="C542" s="17"/>
       <c r="D542" s="17"/>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="I542" s="17"/>
     </row>
-    <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B543" s="17"/>
       <c r="C543" s="17"/>
       <c r="D543" s="17"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="I543" s="17"/>
     </row>
-    <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B544" s="17"/>
       <c r="C544" s="17"/>
       <c r="D544" s="17"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="I544" s="17"/>
     </row>
-    <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B545" s="17"/>
       <c r="C545" s="17"/>
       <c r="D545" s="17"/>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="I545" s="17"/>
     </row>
-    <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B546" s="17"/>
       <c r="C546" s="17"/>
       <c r="D546" s="17"/>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I546" s="17"/>
     </row>
-    <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B547" s="17"/>
       <c r="C547" s="17"/>
       <c r="D547" s="17"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="I547" s="17"/>
     </row>
-    <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B548" s="17"/>
       <c r="C548" s="17"/>
       <c r="D548" s="17"/>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="I548" s="17"/>
     </row>
-    <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B549" s="17"/>
       <c r="C549" s="17"/>
       <c r="D549" s="17"/>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="I549" s="17"/>
     </row>
-    <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B550" s="17"/>
       <c r="C550" s="17"/>
       <c r="D550" s="17"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="I550" s="17"/>
     </row>
-    <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B551" s="17"/>
       <c r="C551" s="17"/>
       <c r="D551" s="17"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I551" s="17"/>
     </row>
-    <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B552" s="17"/>
       <c r="C552" s="17"/>
       <c r="D552" s="17"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="I552" s="17"/>
     </row>
-    <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B553" s="17"/>
       <c r="C553" s="17"/>
       <c r="D553" s="17"/>
@@ -9224,7 +9224,7 @@
       <c r="H553" s="20"/>
       <c r="I553" s="17"/>
     </row>
-    <row r="554" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B554" s="17"/>
       <c r="C554" s="17"/>
       <c r="D554" s="17"/>
@@ -9234,7 +9234,7 @@
       <c r="H554" s="20"/>
       <c r="I554" s="17"/>
     </row>
-    <row r="555" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B555" s="17"/>
       <c r="C555" s="17"/>
       <c r="D555" s="17"/>
@@ -9244,7 +9244,7 @@
       <c r="H555" s="20"/>
       <c r="I555" s="17"/>
     </row>
-    <row r="556" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B556" s="17"/>
       <c r="C556" s="17"/>
       <c r="D556" s="17"/>
@@ -9254,7 +9254,7 @@
       <c r="H556" s="20"/>
       <c r="I556" s="17"/>
     </row>
-    <row r="557" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B557" s="17"/>
       <c r="C557" s="17"/>
       <c r="D557" s="17"/>
@@ -9264,7 +9264,7 @@
       <c r="H557" s="20"/>
       <c r="I557" s="17"/>
     </row>
-    <row r="558" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B558" s="17"/>
       <c r="C558" s="17"/>
       <c r="D558" s="17"/>
@@ -9274,7 +9274,7 @@
       <c r="H558" s="20"/>
       <c r="I558" s="17"/>
     </row>
-    <row r="559" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B559" s="17"/>
       <c r="C559" s="17"/>
       <c r="D559" s="17"/>
@@ -9284,7 +9284,7 @@
       <c r="H559" s="20"/>
       <c r="I559" s="17"/>
     </row>
-    <row r="560" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B560" s="17"/>
       <c r="C560" s="17"/>
       <c r="D560" s="17"/>
@@ -9294,7 +9294,7 @@
       <c r="H560" s="20"/>
       <c r="I560" s="17"/>
     </row>
-    <row r="561" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B561" s="17"/>
       <c r="C561" s="17"/>
       <c r="D561" s="17"/>
@@ -9304,7 +9304,7 @@
       <c r="H561" s="20"/>
       <c r="I561" s="17"/>
     </row>
-    <row r="562" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B562" s="17"/>
       <c r="C562" s="17"/>
       <c r="D562" s="17"/>
@@ -9314,7 +9314,7 @@
       <c r="H562" s="20"/>
       <c r="I562" s="17"/>
     </row>
-    <row r="563" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B563" s="17"/>
       <c r="C563" s="17"/>
       <c r="D563" s="17"/>
@@ -9366,16 +9366,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="25.26953125" style="26" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="26"/>
+    <col min="1" max="1" width="32.83203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="15.609375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="25.27734375" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="8.71875" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>50</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>53</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="26" t="s">
         <v>58</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
         <v>58</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="26" t="s">
         <v>58</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="26" t="s">
         <v>56</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="26" t="s">
         <v>56</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="26" t="s">
         <v>56</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
         <v>56</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="26" t="s">
         <v>63</v>
       </c>
@@ -9528,21 +9528,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="11" customWidth="1"/>
-    <col min="2" max="3" width="18.453125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="6.71875" style="11" customWidth="1"/>
+    <col min="2" max="3" width="18.44140625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="6.71875" style="12" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
       <c r="B2" s="15" t="s">
         <v>1</v>
@@ -9550,13 +9550,13 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
       <c r="B4" s="21" t="s">
         <v>2</v>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D4" s="14"/>
     </row>
-    <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11"/>
       <c r="B5" s="21" t="s">
         <v>12</v>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11"/>
       <c r="B6" s="21" t="s">
         <v>13</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11"/>
       <c r="B7" s="21" t="s">
         <v>14</v>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="B8" s="21" t="s">
         <v>15</v>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11"/>
       <c r="B9" s="21" t="s">
         <v>16</v>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="D9" s="12"/>
     </row>
-    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="B10" s="21" t="s">
         <v>17</v>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21" t="s">
@@ -9634,109 +9634,109 @@
       </c>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="21"/>
       <c r="C12" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="21"/>
       <c r="C13" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="21"/>
       <c r="C14" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="21"/>
       <c r="C15" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="21"/>
       <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="21"/>
       <c r="C19" s="21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="21"/>
       <c r="C20" s="21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="21"/>
       <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="21"/>
       <c r="C22" s="21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="21"/>
       <c r="C23" s="21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="21"/>
       <c r="C24" s="21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="21"/>
       <c r="C25" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="21"/>
       <c r="C26" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="21"/>
       <c r="C27" s="21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="21"/>
       <c r="C28" s="21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="21"/>
       <c r="C29" s="21" t="s">
         <v>42</v>
@@ -9759,12 +9759,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10080,29 +10091,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10129,13 +10133,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Iteration_1/project_tracker.xlsx
+++ b/Iteration_1/project_tracker.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E37017-C8E5-47E6-A310-EB81FA96FED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63A823F-04F1-45EA-8C02-5DA6C448FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
     <sheet name="Meeting Records" sheetId="3" r:id="rId2"/>
-    <sheet name="Setup" sheetId="2" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="5" r:id="rId3"/>
+    <sheet name="Setup" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="CategoryList">Setup!$B$5:$B$29</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="113">
   <si>
     <t>Category</t>
   </si>
@@ -319,6 +320,63 @@
   </si>
   <si>
     <t>Rishabh Agarwal, Richard Nguyen, Mohammad Moustaqim</t>
+  </si>
+  <si>
+    <t>Milestones</t>
+  </si>
+  <si>
+    <t>Complete classes in the class structure diagram</t>
+  </si>
+  <si>
+    <t>Actual Completed</t>
+  </si>
+  <si>
+    <t>Actual Start</t>
+  </si>
+  <si>
+    <t>Planned Completed</t>
+  </si>
+  <si>
+    <t>Planned Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit testing </t>
+  </si>
+  <si>
+    <t>Change classes according to P2 feedback</t>
+  </si>
+  <si>
+    <t>Integrate project from different teams</t>
+  </si>
+  <si>
+    <t>Integration testing</t>
+  </si>
+  <si>
+    <t>Produce gitlog file</t>
+  </si>
+  <si>
+    <t>Record group presentation video</t>
+  </si>
+  <si>
+    <t>Documentation for integration created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete first game </t>
+  </si>
+  <si>
+    <t>Complete second game</t>
+  </si>
+  <si>
+    <t>Complete third game</t>
+  </si>
+  <si>
+    <t>Profile GUI</t>
+  </si>
+  <si>
+    <t>Complete networking stubs</t>
+  </si>
+  <si>
+    <t>Finalize leaderboard and matchmaking logic</t>
   </si>
 </sst>
 </file>
@@ -892,7 +950,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -912,7 +970,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1585,22 +1643,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J563"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.71875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="56.38671875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="21.1640625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" style="18" customWidth="1"/>
-    <col min="5" max="6" width="16.83203125" style="19" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="56.36328125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" style="18" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" style="18" customWidth="1"/>
+    <col min="5" max="6" width="16.81640625" style="19" customWidth="1"/>
     <col min="7" max="8" width="16" style="18" customWidth="1"/>
-    <col min="9" max="9" width="85.609375" style="18" customWidth="1"/>
-    <col min="10" max="10" width="6.71875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="4.1640625" style="2" customWidth="1"/>
-    <col min="12" max="36" width="3.27734375" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="9.109375" style="2"/>
+    <col min="9" max="9" width="85.6328125" style="18" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="4.1796875" style="2" customWidth="1"/>
+    <col min="12" max="36" width="3.26953125" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1612,7 +1670,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="25" t="s">
         <v>11</v>
@@ -1630,7 +1688,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1642,7 +1700,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="16" t="s">
         <v>10</v>
@@ -1670,7 +1728,7 @@
       </c>
       <c r="J4" s="10"/>
     </row>
-    <row r="5" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="17" t="s">
         <v>49</v>
@@ -1697,7 +1755,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="17" t="s">
         <v>43</v>
@@ -1726,7 +1784,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="17" t="s">
         <v>44</v>
@@ -1753,7 +1811,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="17" t="s">
         <v>45</v>
@@ -1782,7 +1840,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>46</v>
@@ -1811,7 +1869,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>47</v>
@@ -1840,7 +1898,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="17" t="s">
         <v>48</v>
@@ -1869,7 +1927,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="17" t="s">
         <v>64</v>
@@ -1898,7 +1956,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" s="5" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="17" t="s">
         <v>68</v>
@@ -1927,7 +1985,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="17" t="s">
         <v>69</v>
@@ -1956,7 +2014,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>70</v>
       </c>
@@ -1981,7 +2039,7 @@
       </c>
       <c r="I15" s="17"/>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>71</v>
       </c>
@@ -2008,7 +2066,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="17" t="s">
         <v>73</v>
       </c>
@@ -2033,7 +2091,7 @@
       </c>
       <c r="I17" s="17"/>
     </row>
-    <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
         <v>74</v>
       </c>
@@ -2060,7 +2118,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="17" t="s">
         <v>75</v>
       </c>
@@ -2087,7 +2145,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="17" t="s">
         <v>77</v>
       </c>
@@ -2114,7 +2172,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="17" t="s">
         <v>78</v>
       </c>
@@ -2139,7 +2197,7 @@
       </c>
       <c r="I21" s="17"/>
     </row>
-    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="17" t="s">
         <v>79</v>
       </c>
@@ -2166,7 +2224,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="17" t="s">
         <v>80</v>
       </c>
@@ -2193,7 +2251,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="17" t="s">
         <v>81</v>
       </c>
@@ -2220,7 +2278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="17" t="s">
         <v>82</v>
       </c>
@@ -2247,7 +2305,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="17" t="s">
         <v>83</v>
       </c>
@@ -2274,7 +2332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
         <v>84</v>
       </c>
@@ -2301,7 +2359,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="17" t="s">
         <v>86</v>
       </c>
@@ -2328,7 +2386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="17" t="s">
         <v>87</v>
       </c>
@@ -2353,7 +2411,7 @@
       </c>
       <c r="I29" s="17"/>
     </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="17" t="s">
         <v>88</v>
       </c>
@@ -2380,7 +2438,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
         <v>89</v>
       </c>
@@ -2405,7 +2463,7 @@
       </c>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="17" t="s">
         <v>90</v>
       </c>
@@ -2430,7 +2488,7 @@
       </c>
       <c r="I32" s="17"/>
     </row>
-    <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="17" t="s">
         <v>91</v>
       </c>
@@ -2455,7 +2513,7 @@
       </c>
       <c r="I33" s="17"/>
     </row>
-    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="17" t="s">
         <v>92</v>
       </c>
@@ -2480,7 +2538,7 @@
       </c>
       <c r="I34" s="17"/>
     </row>
-    <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -2493,7 +2551,7 @@
       </c>
       <c r="I35" s="17"/>
     </row>
-    <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -2506,7 +2564,7 @@
       </c>
       <c r="I36" s="17"/>
     </row>
-    <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -2519,7 +2577,7 @@
       </c>
       <c r="I37" s="17"/>
     </row>
-    <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -2532,7 +2590,7 @@
       </c>
       <c r="I38" s="17"/>
     </row>
-    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -2545,7 +2603,7 @@
       </c>
       <c r="I39" s="17"/>
     </row>
-    <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -2558,7 +2616,7 @@
       </c>
       <c r="I40" s="17"/>
     </row>
-    <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -2571,7 +2629,7 @@
       </c>
       <c r="I41" s="17"/>
     </row>
-    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -2584,7 +2642,7 @@
       </c>
       <c r="I42" s="17"/>
     </row>
-    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -2597,7 +2655,7 @@
       </c>
       <c r="I43" s="17"/>
     </row>
-    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
@@ -2610,7 +2668,7 @@
       </c>
       <c r="I44" s="17"/>
     </row>
-    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -2623,7 +2681,7 @@
       </c>
       <c r="I45" s="17"/>
     </row>
-    <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
@@ -2636,7 +2694,7 @@
       </c>
       <c r="I46" s="17"/>
     </row>
-    <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -2649,7 +2707,7 @@
       </c>
       <c r="I47" s="17"/>
     </row>
-    <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -2662,7 +2720,7 @@
       </c>
       <c r="I48" s="17"/>
     </row>
-    <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -2675,7 +2733,7 @@
       </c>
       <c r="I49" s="17"/>
     </row>
-    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -2688,7 +2746,7 @@
       </c>
       <c r="I50" s="17"/>
     </row>
-    <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -2701,7 +2759,7 @@
       </c>
       <c r="I51" s="17"/>
     </row>
-    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -2714,7 +2772,7 @@
       </c>
       <c r="I52" s="17"/>
     </row>
-    <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -2727,7 +2785,7 @@
       </c>
       <c r="I53" s="17"/>
     </row>
-    <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -2740,7 +2798,7 @@
       </c>
       <c r="I54" s="17"/>
     </row>
-    <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -2753,7 +2811,7 @@
       </c>
       <c r="I55" s="17"/>
     </row>
-    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -2766,7 +2824,7 @@
       </c>
       <c r="I56" s="17"/>
     </row>
-    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -2779,7 +2837,7 @@
       </c>
       <c r="I57" s="17"/>
     </row>
-    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -2792,7 +2850,7 @@
       </c>
       <c r="I58" s="17"/>
     </row>
-    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -2805,7 +2863,7 @@
       </c>
       <c r="I59" s="17"/>
     </row>
-    <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -2818,7 +2876,7 @@
       </c>
       <c r="I60" s="17"/>
     </row>
-    <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
@@ -2831,7 +2889,7 @@
       </c>
       <c r="I61" s="17"/>
     </row>
-    <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -2844,7 +2902,7 @@
       </c>
       <c r="I62" s="17"/>
     </row>
-    <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
@@ -2857,7 +2915,7 @@
       </c>
       <c r="I63" s="17"/>
     </row>
-    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
@@ -2870,7 +2928,7 @@
       </c>
       <c r="I64" s="17"/>
     </row>
-    <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
@@ -2883,7 +2941,7 @@
       </c>
       <c r="I65" s="17"/>
     </row>
-    <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -2896,7 +2954,7 @@
       </c>
       <c r="I66" s="17"/>
     </row>
-    <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17"/>
@@ -2909,7 +2967,7 @@
       </c>
       <c r="I67" s="17"/>
     </row>
-    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
@@ -2922,7 +2980,7 @@
       </c>
       <c r="I68" s="17"/>
     </row>
-    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
@@ -2935,7 +2993,7 @@
       </c>
       <c r="I69" s="17"/>
     </row>
-    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
@@ -2948,7 +3006,7 @@
       </c>
       <c r="I70" s="17"/>
     </row>
-    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -2961,7 +3019,7 @@
       </c>
       <c r="I71" s="17"/>
     </row>
-    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
@@ -2974,7 +3032,7 @@
       </c>
       <c r="I72" s="17"/>
     </row>
-    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
@@ -2987,7 +3045,7 @@
       </c>
       <c r="I73" s="17"/>
     </row>
-    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
@@ -3000,7 +3058,7 @@
       </c>
       <c r="I74" s="17"/>
     </row>
-    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -3013,7 +3071,7 @@
       </c>
       <c r="I75" s="17"/>
     </row>
-    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
@@ -3026,7 +3084,7 @@
       </c>
       <c r="I76" s="17"/>
     </row>
-    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
@@ -3039,7 +3097,7 @@
       </c>
       <c r="I77" s="17"/>
     </row>
-    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
       <c r="D78" s="17"/>
@@ -3052,7 +3110,7 @@
       </c>
       <c r="I78" s="17"/>
     </row>
-    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
@@ -3065,7 +3123,7 @@
       </c>
       <c r="I79" s="17"/>
     </row>
-    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
       <c r="D80" s="17"/>
@@ -3078,7 +3136,7 @@
       </c>
       <c r="I80" s="17"/>
     </row>
-    <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
@@ -3091,7 +3149,7 @@
       </c>
       <c r="I81" s="17"/>
     </row>
-    <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
@@ -3104,7 +3162,7 @@
       </c>
       <c r="I82" s="17"/>
     </row>
-    <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="17"/>
@@ -3117,7 +3175,7 @@
       </c>
       <c r="I83" s="17"/>
     </row>
-    <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -3130,7 +3188,7 @@
       </c>
       <c r="I84" s="17"/>
     </row>
-    <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
       <c r="D85" s="17"/>
@@ -3143,7 +3201,7 @@
       </c>
       <c r="I85" s="17"/>
     </row>
-    <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
       <c r="D86" s="17"/>
@@ -3156,7 +3214,7 @@
       </c>
       <c r="I86" s="17"/>
     </row>
-    <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="17"/>
@@ -3169,7 +3227,7 @@
       </c>
       <c r="I87" s="17"/>
     </row>
-    <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
@@ -3182,7 +3240,7 @@
       </c>
       <c r="I88" s="17"/>
     </row>
-    <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="17"/>
@@ -3195,7 +3253,7 @@
       </c>
       <c r="I89" s="17"/>
     </row>
-    <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
@@ -3208,7 +3266,7 @@
       </c>
       <c r="I90" s="17"/>
     </row>
-    <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
@@ -3221,7 +3279,7 @@
       </c>
       <c r="I91" s="17"/>
     </row>
-    <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="17"/>
@@ -3234,7 +3292,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
       <c r="D93" s="17"/>
@@ -3247,7 +3305,7 @@
       </c>
       <c r="I93" s="17"/>
     </row>
-    <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
       <c r="D94" s="17"/>
@@ -3260,7 +3318,7 @@
       </c>
       <c r="I94" s="17"/>
     </row>
-    <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
       <c r="D95" s="17"/>
@@ -3273,7 +3331,7 @@
       </c>
       <c r="I95" s="17"/>
     </row>
-    <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
       <c r="D96" s="17"/>
@@ -3286,7 +3344,7 @@
       </c>
       <c r="I96" s="17"/>
     </row>
-    <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
       <c r="D97" s="17"/>
@@ -3299,7 +3357,7 @@
       </c>
       <c r="I97" s="17"/>
     </row>
-    <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
       <c r="D98" s="17"/>
@@ -3312,7 +3370,7 @@
       </c>
       <c r="I98" s="17"/>
     </row>
-    <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="17"/>
       <c r="C99" s="17"/>
       <c r="D99" s="17"/>
@@ -3325,7 +3383,7 @@
       </c>
       <c r="I99" s="17"/>
     </row>
-    <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
       <c r="D100" s="17"/>
@@ -3338,7 +3396,7 @@
       </c>
       <c r="I100" s="17"/>
     </row>
-    <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
       <c r="D101" s="17"/>
@@ -3351,7 +3409,7 @@
       </c>
       <c r="I101" s="17"/>
     </row>
-    <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
       <c r="D102" s="17"/>
@@ -3364,7 +3422,7 @@
       </c>
       <c r="I102" s="17"/>
     </row>
-    <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
       <c r="D103" s="17"/>
@@ -3377,7 +3435,7 @@
       </c>
       <c r="I103" s="17"/>
     </row>
-    <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
@@ -3390,7 +3448,7 @@
       </c>
       <c r="I104" s="17"/>
     </row>
-    <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -3403,7 +3461,7 @@
       </c>
       <c r="I105" s="17"/>
     </row>
-    <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -3416,7 +3474,7 @@
       </c>
       <c r="I106" s="17"/>
     </row>
-    <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -3429,7 +3487,7 @@
       </c>
       <c r="I107" s="17"/>
     </row>
-    <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -3442,7 +3500,7 @@
       </c>
       <c r="I108" s="17"/>
     </row>
-    <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -3455,7 +3513,7 @@
       </c>
       <c r="I109" s="17"/>
     </row>
-    <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -3468,7 +3526,7 @@
       </c>
       <c r="I110" s="17"/>
     </row>
-    <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -3481,7 +3539,7 @@
       </c>
       <c r="I111" s="17"/>
     </row>
-    <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -3494,7 +3552,7 @@
       </c>
       <c r="I112" s="17"/>
     </row>
-    <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -3507,7 +3565,7 @@
       </c>
       <c r="I113" s="17"/>
     </row>
-    <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -3520,7 +3578,7 @@
       </c>
       <c r="I114" s="17"/>
     </row>
-    <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -3533,7 +3591,7 @@
       </c>
       <c r="I115" s="17"/>
     </row>
-    <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -3546,7 +3604,7 @@
       </c>
       <c r="I116" s="17"/>
     </row>
-    <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -3559,7 +3617,7 @@
       </c>
       <c r="I117" s="17"/>
     </row>
-    <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -3572,7 +3630,7 @@
       </c>
       <c r="I118" s="17"/>
     </row>
-    <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -3585,7 +3643,7 @@
       </c>
       <c r="I119" s="17"/>
     </row>
-    <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -3598,7 +3656,7 @@
       </c>
       <c r="I120" s="17"/>
     </row>
-    <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -3611,7 +3669,7 @@
       </c>
       <c r="I121" s="17"/>
     </row>
-    <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -3624,7 +3682,7 @@
       </c>
       <c r="I122" s="17"/>
     </row>
-    <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -3637,7 +3695,7 @@
       </c>
       <c r="I123" s="17"/>
     </row>
-    <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -3650,7 +3708,7 @@
       </c>
       <c r="I124" s="17"/>
     </row>
-    <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -3663,7 +3721,7 @@
       </c>
       <c r="I125" s="17"/>
     </row>
-    <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -3676,7 +3734,7 @@
       </c>
       <c r="I126" s="17"/>
     </row>
-    <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -3689,7 +3747,7 @@
       </c>
       <c r="I127" s="17"/>
     </row>
-    <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
       <c r="D128" s="17"/>
@@ -3702,7 +3760,7 @@
       </c>
       <c r="I128" s="17"/>
     </row>
-    <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -3715,7 +3773,7 @@
       </c>
       <c r="I129" s="17"/>
     </row>
-    <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -3728,7 +3786,7 @@
       </c>
       <c r="I130" s="17"/>
     </row>
-    <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -3741,7 +3799,7 @@
       </c>
       <c r="I131" s="17"/>
     </row>
-    <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -3754,7 +3812,7 @@
       </c>
       <c r="I132" s="17"/>
     </row>
-    <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -3767,7 +3825,7 @@
       </c>
       <c r="I133" s="17"/>
     </row>
-    <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -3780,7 +3838,7 @@
       </c>
       <c r="I134" s="17"/>
     </row>
-    <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -3793,7 +3851,7 @@
       </c>
       <c r="I135" s="17"/>
     </row>
-    <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -3806,7 +3864,7 @@
       </c>
       <c r="I136" s="17"/>
     </row>
-    <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -3819,7 +3877,7 @@
       </c>
       <c r="I137" s="17"/>
     </row>
-    <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -3832,7 +3890,7 @@
       </c>
       <c r="I138" s="17"/>
     </row>
-    <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -3845,7 +3903,7 @@
       </c>
       <c r="I139" s="17"/>
     </row>
-    <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
       <c r="D140" s="17"/>
@@ -3858,7 +3916,7 @@
       </c>
       <c r="I140" s="17"/>
     </row>
-    <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
       <c r="D141" s="17"/>
@@ -3871,7 +3929,7 @@
       </c>
       <c r="I141" s="17"/>
     </row>
-    <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
       <c r="D142" s="17"/>
@@ -3884,7 +3942,7 @@
       </c>
       <c r="I142" s="17"/>
     </row>
-    <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="17"/>
       <c r="C143" s="17"/>
       <c r="D143" s="17"/>
@@ -3897,7 +3955,7 @@
       </c>
       <c r="I143" s="17"/>
     </row>
-    <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
       <c r="D144" s="17"/>
@@ -3910,7 +3968,7 @@
       </c>
       <c r="I144" s="17"/>
     </row>
-    <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="17"/>
       <c r="C145" s="17"/>
       <c r="D145" s="17"/>
@@ -3923,7 +3981,7 @@
       </c>
       <c r="I145" s="17"/>
     </row>
-    <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
       <c r="D146" s="17"/>
@@ -3936,7 +3994,7 @@
       </c>
       <c r="I146" s="17"/>
     </row>
-    <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="17"/>
       <c r="C147" s="17"/>
       <c r="D147" s="17"/>
@@ -3949,7 +4007,7 @@
       </c>
       <c r="I147" s="17"/>
     </row>
-    <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
       <c r="D148" s="17"/>
@@ -3962,7 +4020,7 @@
       </c>
       <c r="I148" s="17"/>
     </row>
-    <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="17"/>
       <c r="C149" s="17"/>
       <c r="D149" s="17"/>
@@ -3975,7 +4033,7 @@
       </c>
       <c r="I149" s="17"/>
     </row>
-    <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
@@ -3988,7 +4046,7 @@
       </c>
       <c r="I150" s="17"/>
     </row>
-    <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="17"/>
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
@@ -4001,7 +4059,7 @@
       </c>
       <c r="I151" s="17"/>
     </row>
-    <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
@@ -4014,7 +4072,7 @@
       </c>
       <c r="I152" s="17"/>
     </row>
-    <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B153" s="17"/>
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
@@ -4027,7 +4085,7 @@
       </c>
       <c r="I153" s="17"/>
     </row>
-    <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
@@ -4040,7 +4098,7 @@
       </c>
       <c r="I154" s="17"/>
     </row>
-    <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B155" s="17"/>
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
@@ -4053,7 +4111,7 @@
       </c>
       <c r="I155" s="17"/>
     </row>
-    <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
@@ -4066,7 +4124,7 @@
       </c>
       <c r="I156" s="17"/>
     </row>
-    <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B157" s="17"/>
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
@@ -4079,7 +4137,7 @@
       </c>
       <c r="I157" s="17"/>
     </row>
-    <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
@@ -4092,7 +4150,7 @@
       </c>
       <c r="I158" s="17"/>
     </row>
-    <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B159" s="17"/>
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
@@ -4105,7 +4163,7 @@
       </c>
       <c r="I159" s="17"/>
     </row>
-    <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
@@ -4118,7 +4176,7 @@
       </c>
       <c r="I160" s="17"/>
     </row>
-    <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B161" s="17"/>
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
@@ -4131,7 +4189,7 @@
       </c>
       <c r="I161" s="17"/>
     </row>
-    <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
       <c r="D162" s="17"/>
@@ -4144,7 +4202,7 @@
       </c>
       <c r="I162" s="17"/>
     </row>
-    <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B163" s="17"/>
       <c r="C163" s="17"/>
       <c r="D163" s="17"/>
@@ -4157,7 +4215,7 @@
       </c>
       <c r="I163" s="17"/>
     </row>
-    <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
       <c r="D164" s="17"/>
@@ -4170,7 +4228,7 @@
       </c>
       <c r="I164" s="17"/>
     </row>
-    <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B165" s="17"/>
       <c r="C165" s="17"/>
       <c r="D165" s="17"/>
@@ -4183,7 +4241,7 @@
       </c>
       <c r="I165" s="17"/>
     </row>
-    <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
       <c r="D166" s="17"/>
@@ -4196,7 +4254,7 @@
       </c>
       <c r="I166" s="17"/>
     </row>
-    <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B167" s="17"/>
       <c r="C167" s="17"/>
       <c r="D167" s="17"/>
@@ -4209,7 +4267,7 @@
       </c>
       <c r="I167" s="17"/>
     </row>
-    <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
       <c r="D168" s="17"/>
@@ -4222,7 +4280,7 @@
       </c>
       <c r="I168" s="17"/>
     </row>
-    <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B169" s="17"/>
       <c r="C169" s="17"/>
       <c r="D169" s="17"/>
@@ -4235,7 +4293,7 @@
       </c>
       <c r="I169" s="17"/>
     </row>
-    <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
       <c r="D170" s="17"/>
@@ -4248,7 +4306,7 @@
       </c>
       <c r="I170" s="17"/>
     </row>
-    <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B171" s="17"/>
       <c r="C171" s="17"/>
       <c r="D171" s="17"/>
@@ -4261,7 +4319,7 @@
       </c>
       <c r="I171" s="17"/>
     </row>
-    <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
       <c r="D172" s="17"/>
@@ -4274,7 +4332,7 @@
       </c>
       <c r="I172" s="17"/>
     </row>
-    <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B173" s="17"/>
       <c r="C173" s="17"/>
       <c r="D173" s="17"/>
@@ -4287,7 +4345,7 @@
       </c>
       <c r="I173" s="17"/>
     </row>
-    <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
       <c r="D174" s="17"/>
@@ -4300,7 +4358,7 @@
       </c>
       <c r="I174" s="17"/>
     </row>
-    <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B175" s="17"/>
       <c r="C175" s="17"/>
       <c r="D175" s="17"/>
@@ -4313,7 +4371,7 @@
       </c>
       <c r="I175" s="17"/>
     </row>
-    <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
       <c r="D176" s="17"/>
@@ -4326,7 +4384,7 @@
       </c>
       <c r="I176" s="17"/>
     </row>
-    <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B177" s="17"/>
       <c r="C177" s="17"/>
       <c r="D177" s="17"/>
@@ -4339,7 +4397,7 @@
       </c>
       <c r="I177" s="17"/>
     </row>
-    <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
       <c r="D178" s="17"/>
@@ -4352,7 +4410,7 @@
       </c>
       <c r="I178" s="17"/>
     </row>
-    <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
@@ -4365,7 +4423,7 @@
       </c>
       <c r="I179" s="17"/>
     </row>
-    <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
       <c r="D180" s="17"/>
@@ -4378,7 +4436,7 @@
       </c>
       <c r="I180" s="17"/>
     </row>
-    <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
       <c r="D181" s="17"/>
@@ -4391,7 +4449,7 @@
       </c>
       <c r="I181" s="17"/>
     </row>
-    <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
       <c r="D182" s="17"/>
@@ -4404,7 +4462,7 @@
       </c>
       <c r="I182" s="17"/>
     </row>
-    <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
       <c r="D183" s="17"/>
@@ -4417,7 +4475,7 @@
       </c>
       <c r="I183" s="17"/>
     </row>
-    <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
       <c r="D184" s="17"/>
@@ -4430,7 +4488,7 @@
       </c>
       <c r="I184" s="17"/>
     </row>
-    <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
@@ -4443,7 +4501,7 @@
       </c>
       <c r="I185" s="17"/>
     </row>
-    <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
       <c r="D186" s="17"/>
@@ -4456,7 +4514,7 @@
       </c>
       <c r="I186" s="17"/>
     </row>
-    <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
       <c r="D187" s="17"/>
@@ -4469,7 +4527,7 @@
       </c>
       <c r="I187" s="17"/>
     </row>
-    <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
       <c r="D188" s="17"/>
@@ -4482,7 +4540,7 @@
       </c>
       <c r="I188" s="17"/>
     </row>
-    <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
       <c r="D189" s="17"/>
@@ -4495,7 +4553,7 @@
       </c>
       <c r="I189" s="17"/>
     </row>
-    <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
       <c r="D190" s="17"/>
@@ -4508,7 +4566,7 @@
       </c>
       <c r="I190" s="17"/>
     </row>
-    <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
@@ -4521,7 +4579,7 @@
       </c>
       <c r="I191" s="17"/>
     </row>
-    <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
       <c r="D192" s="17"/>
@@ -4534,7 +4592,7 @@
       </c>
       <c r="I192" s="17"/>
     </row>
-    <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="17"/>
       <c r="C193" s="17"/>
       <c r="D193" s="17"/>
@@ -4547,7 +4605,7 @@
       </c>
       <c r="I193" s="17"/>
     </row>
-    <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
       <c r="D194" s="17"/>
@@ -4560,7 +4618,7 @@
       </c>
       <c r="I194" s="17"/>
     </row>
-    <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
       <c r="D195" s="17"/>
@@ -4573,7 +4631,7 @@
       </c>
       <c r="I195" s="17"/>
     </row>
-    <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
@@ -4586,7 +4644,7 @@
       </c>
       <c r="I196" s="17"/>
     </row>
-    <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
       <c r="D197" s="17"/>
@@ -4599,7 +4657,7 @@
       </c>
       <c r="I197" s="17"/>
     </row>
-    <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
       <c r="D198" s="17"/>
@@ -4612,7 +4670,7 @@
       </c>
       <c r="I198" s="17"/>
     </row>
-    <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B199" s="17"/>
       <c r="C199" s="17"/>
       <c r="D199" s="17"/>
@@ -4625,7 +4683,7 @@
       </c>
       <c r="I199" s="17"/>
     </row>
-    <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
       <c r="D200" s="17"/>
@@ -4638,7 +4696,7 @@
       </c>
       <c r="I200" s="17"/>
     </row>
-    <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
       <c r="D201" s="17"/>
@@ -4651,7 +4709,7 @@
       </c>
       <c r="I201" s="17"/>
     </row>
-    <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
@@ -4664,7 +4722,7 @@
       </c>
       <c r="I202" s="17"/>
     </row>
-    <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B203" s="17"/>
       <c r="C203" s="17"/>
       <c r="D203" s="17"/>
@@ -4677,7 +4735,7 @@
       </c>
       <c r="I203" s="17"/>
     </row>
-    <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
       <c r="D204" s="17"/>
@@ -4690,7 +4748,7 @@
       </c>
       <c r="I204" s="17"/>
     </row>
-    <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
       <c r="D205" s="17"/>
@@ -4703,7 +4761,7 @@
       </c>
       <c r="I205" s="17"/>
     </row>
-    <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
       <c r="D206" s="17"/>
@@ -4716,7 +4774,7 @@
       </c>
       <c r="I206" s="17"/>
     </row>
-    <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" s="17"/>
       <c r="C207" s="17"/>
       <c r="D207" s="17"/>
@@ -4729,7 +4787,7 @@
       </c>
       <c r="I207" s="17"/>
     </row>
-    <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
       <c r="D208" s="17"/>
@@ -4742,7 +4800,7 @@
       </c>
       <c r="I208" s="17"/>
     </row>
-    <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
       <c r="D209" s="17"/>
@@ -4755,7 +4813,7 @@
       </c>
       <c r="I209" s="17"/>
     </row>
-    <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
       <c r="D210" s="17"/>
@@ -4768,7 +4826,7 @@
       </c>
       <c r="I210" s="17"/>
     </row>
-    <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B211" s="17"/>
       <c r="C211" s="17"/>
       <c r="D211" s="17"/>
@@ -4781,7 +4839,7 @@
       </c>
       <c r="I211" s="17"/>
     </row>
-    <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B212" s="17"/>
       <c r="C212" s="17"/>
       <c r="D212" s="17"/>
@@ -4794,7 +4852,7 @@
       </c>
       <c r="I212" s="17"/>
     </row>
-    <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B213" s="17"/>
       <c r="C213" s="17"/>
       <c r="D213" s="17"/>
@@ -4807,7 +4865,7 @@
       </c>
       <c r="I213" s="17"/>
     </row>
-    <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="17"/>
       <c r="C214" s="17"/>
       <c r="D214" s="17"/>
@@ -4820,7 +4878,7 @@
       </c>
       <c r="I214" s="17"/>
     </row>
-    <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B215" s="17"/>
       <c r="C215" s="17"/>
       <c r="D215" s="17"/>
@@ -4833,7 +4891,7 @@
       </c>
       <c r="I215" s="17"/>
     </row>
-    <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B216" s="17"/>
       <c r="C216" s="17"/>
       <c r="D216" s="17"/>
@@ -4846,7 +4904,7 @@
       </c>
       <c r="I216" s="17"/>
     </row>
-    <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B217" s="17"/>
       <c r="C217" s="17"/>
       <c r="D217" s="17"/>
@@ -4859,7 +4917,7 @@
       </c>
       <c r="I217" s="17"/>
     </row>
-    <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B218" s="17"/>
       <c r="C218" s="17"/>
       <c r="D218" s="17"/>
@@ -4872,7 +4930,7 @@
       </c>
       <c r="I218" s="17"/>
     </row>
-    <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B219" s="17"/>
       <c r="C219" s="17"/>
       <c r="D219" s="17"/>
@@ -4885,7 +4943,7 @@
       </c>
       <c r="I219" s="17"/>
     </row>
-    <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
       <c r="D220" s="17"/>
@@ -4898,7 +4956,7 @@
       </c>
       <c r="I220" s="17"/>
     </row>
-    <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B221" s="17"/>
       <c r="C221" s="17"/>
       <c r="D221" s="17"/>
@@ -4911,7 +4969,7 @@
       </c>
       <c r="I221" s="17"/>
     </row>
-    <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
       <c r="D222" s="17"/>
@@ -4924,7 +4982,7 @@
       </c>
       <c r="I222" s="17"/>
     </row>
-    <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B223" s="17"/>
       <c r="C223" s="17"/>
       <c r="D223" s="17"/>
@@ -4937,7 +4995,7 @@
       </c>
       <c r="I223" s="17"/>
     </row>
-    <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" s="17"/>
       <c r="C224" s="17"/>
       <c r="D224" s="17"/>
@@ -4950,7 +5008,7 @@
       </c>
       <c r="I224" s="17"/>
     </row>
-    <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B225" s="17"/>
       <c r="C225" s="17"/>
       <c r="D225" s="17"/>
@@ -4963,7 +5021,7 @@
       </c>
       <c r="I225" s="17"/>
     </row>
-    <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B226" s="17"/>
       <c r="C226" s="17"/>
       <c r="D226" s="17"/>
@@ -4976,7 +5034,7 @@
       </c>
       <c r="I226" s="17"/>
     </row>
-    <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
       <c r="D227" s="17"/>
@@ -4989,7 +5047,7 @@
       </c>
       <c r="I227" s="17"/>
     </row>
-    <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
       <c r="D228" s="17"/>
@@ -5002,7 +5060,7 @@
       </c>
       <c r="I228" s="17"/>
     </row>
-    <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
       <c r="D229" s="17"/>
@@ -5015,7 +5073,7 @@
       </c>
       <c r="I229" s="17"/>
     </row>
-    <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" s="17"/>
       <c r="C230" s="17"/>
       <c r="D230" s="17"/>
@@ -5028,7 +5086,7 @@
       </c>
       <c r="I230" s="17"/>
     </row>
-    <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="17"/>
       <c r="C231" s="17"/>
       <c r="D231" s="17"/>
@@ -5041,7 +5099,7 @@
       </c>
       <c r="I231" s="17"/>
     </row>
-    <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="17"/>
       <c r="C232" s="17"/>
       <c r="D232" s="17"/>
@@ -5054,7 +5112,7 @@
       </c>
       <c r="I232" s="17"/>
     </row>
-    <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="17"/>
       <c r="C233" s="17"/>
       <c r="D233" s="17"/>
@@ -5067,7 +5125,7 @@
       </c>
       <c r="I233" s="17"/>
     </row>
-    <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="17"/>
       <c r="C234" s="17"/>
       <c r="D234" s="17"/>
@@ -5080,7 +5138,7 @@
       </c>
       <c r="I234" s="17"/>
     </row>
-    <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="17"/>
       <c r="C235" s="17"/>
       <c r="D235" s="17"/>
@@ -5093,7 +5151,7 @@
       </c>
       <c r="I235" s="17"/>
     </row>
-    <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" s="17"/>
       <c r="C236" s="17"/>
       <c r="D236" s="17"/>
@@ -5106,7 +5164,7 @@
       </c>
       <c r="I236" s="17"/>
     </row>
-    <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" s="17"/>
       <c r="C237" s="17"/>
       <c r="D237" s="17"/>
@@ -5119,7 +5177,7 @@
       </c>
       <c r="I237" s="17"/>
     </row>
-    <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B238" s="17"/>
       <c r="C238" s="17"/>
       <c r="D238" s="17"/>
@@ -5132,7 +5190,7 @@
       </c>
       <c r="I238" s="17"/>
     </row>
-    <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" s="17"/>
       <c r="C239" s="17"/>
       <c r="D239" s="17"/>
@@ -5145,7 +5203,7 @@
       </c>
       <c r="I239" s="17"/>
     </row>
-    <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B240" s="17"/>
       <c r="C240" s="17"/>
       <c r="D240" s="17"/>
@@ -5158,7 +5216,7 @@
       </c>
       <c r="I240" s="17"/>
     </row>
-    <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
       <c r="D241" s="17"/>
@@ -5171,7 +5229,7 @@
       </c>
       <c r="I241" s="17"/>
     </row>
-    <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
       <c r="D242" s="17"/>
@@ -5184,7 +5242,7 @@
       </c>
       <c r="I242" s="17"/>
     </row>
-    <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
       <c r="D243" s="17"/>
@@ -5197,7 +5255,7 @@
       </c>
       <c r="I243" s="17"/>
     </row>
-    <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
       <c r="D244" s="17"/>
@@ -5210,7 +5268,7 @@
       </c>
       <c r="I244" s="17"/>
     </row>
-    <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B245" s="17"/>
       <c r="C245" s="17"/>
       <c r="D245" s="17"/>
@@ -5223,7 +5281,7 @@
       </c>
       <c r="I245" s="17"/>
     </row>
-    <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
       <c r="D246" s="17"/>
@@ -5236,7 +5294,7 @@
       </c>
       <c r="I246" s="17"/>
     </row>
-    <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B247" s="17"/>
       <c r="C247" s="17"/>
       <c r="D247" s="17"/>
@@ -5249,7 +5307,7 @@
       </c>
       <c r="I247" s="17"/>
     </row>
-    <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
       <c r="D248" s="17"/>
@@ -5262,7 +5320,7 @@
       </c>
       <c r="I248" s="17"/>
     </row>
-    <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B249" s="17"/>
       <c r="C249" s="17"/>
       <c r="D249" s="17"/>
@@ -5275,7 +5333,7 @@
       </c>
       <c r="I249" s="17"/>
     </row>
-    <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
       <c r="D250" s="17"/>
@@ -5288,7 +5346,7 @@
       </c>
       <c r="I250" s="17"/>
     </row>
-    <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B251" s="17"/>
       <c r="C251" s="17"/>
       <c r="D251" s="17"/>
@@ -5301,7 +5359,7 @@
       </c>
       <c r="I251" s="17"/>
     </row>
-    <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
       <c r="D252" s="17"/>
@@ -5314,7 +5372,7 @@
       </c>
       <c r="I252" s="17"/>
     </row>
-    <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
       <c r="D253" s="17"/>
@@ -5327,7 +5385,7 @@
       </c>
       <c r="I253" s="17"/>
     </row>
-    <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
       <c r="D254" s="17"/>
@@ -5340,7 +5398,7 @@
       </c>
       <c r="I254" s="17"/>
     </row>
-    <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B255" s="17"/>
       <c r="C255" s="17"/>
       <c r="D255" s="17"/>
@@ -5353,7 +5411,7 @@
       </c>
       <c r="I255" s="17"/>
     </row>
-    <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
       <c r="D256" s="17"/>
@@ -5366,7 +5424,7 @@
       </c>
       <c r="I256" s="17"/>
     </row>
-    <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="17"/>
       <c r="C257" s="17"/>
       <c r="D257" s="17"/>
@@ -5379,7 +5437,7 @@
       </c>
       <c r="I257" s="17"/>
     </row>
-    <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
       <c r="D258" s="17"/>
@@ -5392,7 +5450,7 @@
       </c>
       <c r="I258" s="17"/>
     </row>
-    <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
       <c r="D259" s="17"/>
@@ -5405,7 +5463,7 @@
       </c>
       <c r="I259" s="17"/>
     </row>
-    <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
       <c r="D260" s="17"/>
@@ -5418,7 +5476,7 @@
       </c>
       <c r="I260" s="17"/>
     </row>
-    <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
       <c r="D261" s="17"/>
@@ -5431,7 +5489,7 @@
       </c>
       <c r="I261" s="17"/>
     </row>
-    <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B262" s="17"/>
       <c r="C262" s="17"/>
       <c r="D262" s="17"/>
@@ -5444,7 +5502,7 @@
       </c>
       <c r="I262" s="17"/>
     </row>
-    <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
       <c r="D263" s="17"/>
@@ -5457,7 +5515,7 @@
       </c>
       <c r="I263" s="17"/>
     </row>
-    <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
       <c r="D264" s="17"/>
@@ -5470,7 +5528,7 @@
       </c>
       <c r="I264" s="17"/>
     </row>
-    <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B265" s="17"/>
       <c r="C265" s="17"/>
       <c r="D265" s="17"/>
@@ -5483,7 +5541,7 @@
       </c>
       <c r="I265" s="17"/>
     </row>
-    <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
       <c r="D266" s="17"/>
@@ -5496,7 +5554,7 @@
       </c>
       <c r="I266" s="17"/>
     </row>
-    <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B267" s="17"/>
       <c r="C267" s="17"/>
       <c r="D267" s="17"/>
@@ -5509,7 +5567,7 @@
       </c>
       <c r="I267" s="17"/>
     </row>
-    <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
       <c r="D268" s="17"/>
@@ -5522,7 +5580,7 @@
       </c>
       <c r="I268" s="17"/>
     </row>
-    <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
       <c r="D269" s="17"/>
@@ -5535,7 +5593,7 @@
       </c>
       <c r="I269" s="17"/>
     </row>
-    <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
       <c r="D270" s="17"/>
@@ -5548,7 +5606,7 @@
       </c>
       <c r="I270" s="17"/>
     </row>
-    <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
       <c r="D271" s="17"/>
@@ -5561,7 +5619,7 @@
       </c>
       <c r="I271" s="17"/>
     </row>
-    <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
       <c r="D272" s="17"/>
@@ -5574,7 +5632,7 @@
       </c>
       <c r="I272" s="17"/>
     </row>
-    <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
       <c r="D273" s="17"/>
@@ -5587,7 +5645,7 @@
       </c>
       <c r="I273" s="17"/>
     </row>
-    <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
       <c r="D274" s="17"/>
@@ -5600,7 +5658,7 @@
       </c>
       <c r="I274" s="17"/>
     </row>
-    <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
       <c r="D275" s="17"/>
@@ -5613,7 +5671,7 @@
       </c>
       <c r="I275" s="17"/>
     </row>
-    <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
       <c r="D276" s="17"/>
@@ -5626,7 +5684,7 @@
       </c>
       <c r="I276" s="17"/>
     </row>
-    <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B277" s="17"/>
       <c r="C277" s="17"/>
       <c r="D277" s="17"/>
@@ -5639,7 +5697,7 @@
       </c>
       <c r="I277" s="17"/>
     </row>
-    <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
       <c r="D278" s="17"/>
@@ -5652,7 +5710,7 @@
       </c>
       <c r="I278" s="17"/>
     </row>
-    <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B279" s="17"/>
       <c r="C279" s="17"/>
       <c r="D279" s="17"/>
@@ -5665,7 +5723,7 @@
       </c>
       <c r="I279" s="17"/>
     </row>
-    <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B280" s="17"/>
       <c r="C280" s="17"/>
       <c r="D280" s="17"/>
@@ -5678,7 +5736,7 @@
       </c>
       <c r="I280" s="17"/>
     </row>
-    <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B281" s="17"/>
       <c r="C281" s="17"/>
       <c r="D281" s="17"/>
@@ -5691,7 +5749,7 @@
       </c>
       <c r="I281" s="17"/>
     </row>
-    <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B282" s="17"/>
       <c r="C282" s="17"/>
       <c r="D282" s="17"/>
@@ -5704,7 +5762,7 @@
       </c>
       <c r="I282" s="17"/>
     </row>
-    <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
       <c r="D283" s="17"/>
@@ -5717,7 +5775,7 @@
       </c>
       <c r="I283" s="17"/>
     </row>
-    <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B284" s="17"/>
       <c r="C284" s="17"/>
       <c r="D284" s="17"/>
@@ -5730,7 +5788,7 @@
       </c>
       <c r="I284" s="17"/>
     </row>
-    <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B285" s="17"/>
       <c r="C285" s="17"/>
       <c r="D285" s="17"/>
@@ -5743,7 +5801,7 @@
       </c>
       <c r="I285" s="17"/>
     </row>
-    <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B286" s="17"/>
       <c r="C286" s="17"/>
       <c r="D286" s="17"/>
@@ -5756,7 +5814,7 @@
       </c>
       <c r="I286" s="17"/>
     </row>
-    <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B287" s="17"/>
       <c r="C287" s="17"/>
       <c r="D287" s="17"/>
@@ -5769,7 +5827,7 @@
       </c>
       <c r="I287" s="17"/>
     </row>
-    <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B288" s="17"/>
       <c r="C288" s="17"/>
       <c r="D288" s="17"/>
@@ -5782,7 +5840,7 @@
       </c>
       <c r="I288" s="17"/>
     </row>
-    <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B289" s="17"/>
       <c r="C289" s="17"/>
       <c r="D289" s="17"/>
@@ -5795,7 +5853,7 @@
       </c>
       <c r="I289" s="17"/>
     </row>
-    <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B290" s="17"/>
       <c r="C290" s="17"/>
       <c r="D290" s="17"/>
@@ -5808,7 +5866,7 @@
       </c>
       <c r="I290" s="17"/>
     </row>
-    <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B291" s="17"/>
       <c r="C291" s="17"/>
       <c r="D291" s="17"/>
@@ -5821,7 +5879,7 @@
       </c>
       <c r="I291" s="17"/>
     </row>
-    <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B292" s="17"/>
       <c r="C292" s="17"/>
       <c r="D292" s="17"/>
@@ -5834,7 +5892,7 @@
       </c>
       <c r="I292" s="17"/>
     </row>
-    <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B293" s="17"/>
       <c r="C293" s="17"/>
       <c r="D293" s="17"/>
@@ -5847,7 +5905,7 @@
       </c>
       <c r="I293" s="17"/>
     </row>
-    <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B294" s="17"/>
       <c r="C294" s="17"/>
       <c r="D294" s="17"/>
@@ -5860,7 +5918,7 @@
       </c>
       <c r="I294" s="17"/>
     </row>
-    <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B295" s="17"/>
       <c r="C295" s="17"/>
       <c r="D295" s="17"/>
@@ -5873,7 +5931,7 @@
       </c>
       <c r="I295" s="17"/>
     </row>
-    <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B296" s="17"/>
       <c r="C296" s="17"/>
       <c r="D296" s="17"/>
@@ -5886,7 +5944,7 @@
       </c>
       <c r="I296" s="17"/>
     </row>
-    <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B297" s="17"/>
       <c r="C297" s="17"/>
       <c r="D297" s="17"/>
@@ -5899,7 +5957,7 @@
       </c>
       <c r="I297" s="17"/>
     </row>
-    <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B298" s="17"/>
       <c r="C298" s="17"/>
       <c r="D298" s="17"/>
@@ -5912,7 +5970,7 @@
       </c>
       <c r="I298" s="17"/>
     </row>
-    <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B299" s="17"/>
       <c r="C299" s="17"/>
       <c r="D299" s="17"/>
@@ -5925,7 +5983,7 @@
       </c>
       <c r="I299" s="17"/>
     </row>
-    <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
       <c r="D300" s="17"/>
@@ -5938,7 +5996,7 @@
       </c>
       <c r="I300" s="17"/>
     </row>
-    <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
       <c r="D301" s="17"/>
@@ -5951,7 +6009,7 @@
       </c>
       <c r="I301" s="17"/>
     </row>
-    <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B302" s="17"/>
       <c r="C302" s="17"/>
       <c r="D302" s="17"/>
@@ -5964,7 +6022,7 @@
       </c>
       <c r="I302" s="17"/>
     </row>
-    <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B303" s="17"/>
       <c r="C303" s="17"/>
       <c r="D303" s="17"/>
@@ -5977,7 +6035,7 @@
       </c>
       <c r="I303" s="17"/>
     </row>
-    <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B304" s="17"/>
       <c r="C304" s="17"/>
       <c r="D304" s="17"/>
@@ -5990,7 +6048,7 @@
       </c>
       <c r="I304" s="17"/>
     </row>
-    <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B305" s="17"/>
       <c r="C305" s="17"/>
       <c r="D305" s="17"/>
@@ -6003,7 +6061,7 @@
       </c>
       <c r="I305" s="17"/>
     </row>
-    <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
       <c r="D306" s="17"/>
@@ -6016,7 +6074,7 @@
       </c>
       <c r="I306" s="17"/>
     </row>
-    <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
       <c r="D307" s="17"/>
@@ -6029,7 +6087,7 @@
       </c>
       <c r="I307" s="17"/>
     </row>
-    <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
       <c r="D308" s="17"/>
@@ -6042,7 +6100,7 @@
       </c>
       <c r="I308" s="17"/>
     </row>
-    <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
       <c r="D309" s="17"/>
@@ -6055,7 +6113,7 @@
       </c>
       <c r="I309" s="17"/>
     </row>
-    <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
       <c r="D310" s="17"/>
@@ -6068,7 +6126,7 @@
       </c>
       <c r="I310" s="17"/>
     </row>
-    <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B311" s="17"/>
       <c r="C311" s="17"/>
       <c r="D311" s="17"/>
@@ -6081,7 +6139,7 @@
       </c>
       <c r="I311" s="17"/>
     </row>
-    <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B312" s="17"/>
       <c r="C312" s="17"/>
       <c r="D312" s="17"/>
@@ -6094,7 +6152,7 @@
       </c>
       <c r="I312" s="17"/>
     </row>
-    <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
       <c r="D313" s="17"/>
@@ -6107,7 +6165,7 @@
       </c>
       <c r="I313" s="17"/>
     </row>
-    <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
       <c r="D314" s="17"/>
@@ -6120,7 +6178,7 @@
       </c>
       <c r="I314" s="17"/>
     </row>
-    <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B315" s="17"/>
       <c r="C315" s="17"/>
       <c r="D315" s="17"/>
@@ -6133,7 +6191,7 @@
       </c>
       <c r="I315" s="17"/>
     </row>
-    <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B316" s="17"/>
       <c r="C316" s="17"/>
       <c r="D316" s="17"/>
@@ -6146,7 +6204,7 @@
       </c>
       <c r="I316" s="17"/>
     </row>
-    <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B317" s="17"/>
       <c r="C317" s="17"/>
       <c r="D317" s="17"/>
@@ -6159,7 +6217,7 @@
       </c>
       <c r="I317" s="17"/>
     </row>
-    <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>
       <c r="D318" s="17"/>
@@ -6172,7 +6230,7 @@
       </c>
       <c r="I318" s="17"/>
     </row>
-    <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B319" s="17"/>
       <c r="C319" s="17"/>
       <c r="D319" s="17"/>
@@ -6185,7 +6243,7 @@
       </c>
       <c r="I319" s="17"/>
     </row>
-    <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B320" s="17"/>
       <c r="C320" s="17"/>
       <c r="D320" s="17"/>
@@ -6198,7 +6256,7 @@
       </c>
       <c r="I320" s="17"/>
     </row>
-    <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B321" s="17"/>
       <c r="C321" s="17"/>
       <c r="D321" s="17"/>
@@ -6211,7 +6269,7 @@
       </c>
       <c r="I321" s="17"/>
     </row>
-    <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B322" s="17"/>
       <c r="C322" s="17"/>
       <c r="D322" s="17"/>
@@ -6224,7 +6282,7 @@
       </c>
       <c r="I322" s="17"/>
     </row>
-    <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B323" s="17"/>
       <c r="C323" s="17"/>
       <c r="D323" s="17"/>
@@ -6237,7 +6295,7 @@
       </c>
       <c r="I323" s="17"/>
     </row>
-    <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B324" s="17"/>
       <c r="C324" s="17"/>
       <c r="D324" s="17"/>
@@ -6250,7 +6308,7 @@
       </c>
       <c r="I324" s="17"/>
     </row>
-    <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
       <c r="D325" s="17"/>
@@ -6263,7 +6321,7 @@
       </c>
       <c r="I325" s="17"/>
     </row>
-    <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B326" s="17"/>
       <c r="C326" s="17"/>
       <c r="D326" s="17"/>
@@ -6276,7 +6334,7 @@
       </c>
       <c r="I326" s="17"/>
     </row>
-    <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B327" s="17"/>
       <c r="C327" s="17"/>
       <c r="D327" s="17"/>
@@ -6289,7 +6347,7 @@
       </c>
       <c r="I327" s="17"/>
     </row>
-    <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B328" s="17"/>
       <c r="C328" s="17"/>
       <c r="D328" s="17"/>
@@ -6302,7 +6360,7 @@
       </c>
       <c r="I328" s="17"/>
     </row>
-    <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B329" s="17"/>
       <c r="C329" s="17"/>
       <c r="D329" s="17"/>
@@ -6315,7 +6373,7 @@
       </c>
       <c r="I329" s="17"/>
     </row>
-    <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B330" s="17"/>
       <c r="C330" s="17"/>
       <c r="D330" s="17"/>
@@ -6328,7 +6386,7 @@
       </c>
       <c r="I330" s="17"/>
     </row>
-    <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B331" s="17"/>
       <c r="C331" s="17"/>
       <c r="D331" s="17"/>
@@ -6341,7 +6399,7 @@
       </c>
       <c r="I331" s="17"/>
     </row>
-    <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B332" s="17"/>
       <c r="C332" s="17"/>
       <c r="D332" s="17"/>
@@ -6354,7 +6412,7 @@
       </c>
       <c r="I332" s="17"/>
     </row>
-    <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B333" s="17"/>
       <c r="C333" s="17"/>
       <c r="D333" s="17"/>
@@ -6367,7 +6425,7 @@
       </c>
       <c r="I333" s="17"/>
     </row>
-    <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B334" s="17"/>
       <c r="C334" s="17"/>
       <c r="D334" s="17"/>
@@ -6380,7 +6438,7 @@
       </c>
       <c r="I334" s="17"/>
     </row>
-    <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B335" s="17"/>
       <c r="C335" s="17"/>
       <c r="D335" s="17"/>
@@ -6393,7 +6451,7 @@
       </c>
       <c r="I335" s="17"/>
     </row>
-    <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" s="17"/>
       <c r="C336" s="17"/>
       <c r="D336" s="17"/>
@@ -6406,7 +6464,7 @@
       </c>
       <c r="I336" s="17"/>
     </row>
-    <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B337" s="17"/>
       <c r="C337" s="17"/>
       <c r="D337" s="17"/>
@@ -6419,7 +6477,7 @@
       </c>
       <c r="I337" s="17"/>
     </row>
-    <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" s="17"/>
       <c r="C338" s="17"/>
       <c r="D338" s="17"/>
@@ -6432,7 +6490,7 @@
       </c>
       <c r="I338" s="17"/>
     </row>
-    <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B339" s="17"/>
       <c r="C339" s="17"/>
       <c r="D339" s="17"/>
@@ -6445,7 +6503,7 @@
       </c>
       <c r="I339" s="17"/>
     </row>
-    <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B340" s="17"/>
       <c r="C340" s="17"/>
       <c r="D340" s="17"/>
@@ -6458,7 +6516,7 @@
       </c>
       <c r="I340" s="17"/>
     </row>
-    <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B341" s="17"/>
       <c r="C341" s="17"/>
       <c r="D341" s="17"/>
@@ -6471,7 +6529,7 @@
       </c>
       <c r="I341" s="17"/>
     </row>
-    <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B342" s="17"/>
       <c r="C342" s="17"/>
       <c r="D342" s="17"/>
@@ -6484,7 +6542,7 @@
       </c>
       <c r="I342" s="17"/>
     </row>
-    <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B343" s="17"/>
       <c r="C343" s="17"/>
       <c r="D343" s="17"/>
@@ -6497,7 +6555,7 @@
       </c>
       <c r="I343" s="17"/>
     </row>
-    <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B344" s="17"/>
       <c r="C344" s="17"/>
       <c r="D344" s="17"/>
@@ -6510,7 +6568,7 @@
       </c>
       <c r="I344" s="17"/>
     </row>
-    <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B345" s="17"/>
       <c r="C345" s="17"/>
       <c r="D345" s="17"/>
@@ -6523,7 +6581,7 @@
       </c>
       <c r="I345" s="17"/>
     </row>
-    <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B346" s="17"/>
       <c r="C346" s="17"/>
       <c r="D346" s="17"/>
@@ -6536,7 +6594,7 @@
       </c>
       <c r="I346" s="17"/>
     </row>
-    <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B347" s="17"/>
       <c r="C347" s="17"/>
       <c r="D347" s="17"/>
@@ -6549,7 +6607,7 @@
       </c>
       <c r="I347" s="17"/>
     </row>
-    <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B348" s="17"/>
       <c r="C348" s="17"/>
       <c r="D348" s="17"/>
@@ -6562,7 +6620,7 @@
       </c>
       <c r="I348" s="17"/>
     </row>
-    <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B349" s="17"/>
       <c r="C349" s="17"/>
       <c r="D349" s="17"/>
@@ -6575,7 +6633,7 @@
       </c>
       <c r="I349" s="17"/>
     </row>
-    <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B350" s="17"/>
       <c r="C350" s="17"/>
       <c r="D350" s="17"/>
@@ -6588,7 +6646,7 @@
       </c>
       <c r="I350" s="17"/>
     </row>
-    <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B351" s="17"/>
       <c r="C351" s="17"/>
       <c r="D351" s="17"/>
@@ -6601,7 +6659,7 @@
       </c>
       <c r="I351" s="17"/>
     </row>
-    <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B352" s="17"/>
       <c r="C352" s="17"/>
       <c r="D352" s="17"/>
@@ -6614,7 +6672,7 @@
       </c>
       <c r="I352" s="17"/>
     </row>
-    <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B353" s="17"/>
       <c r="C353" s="17"/>
       <c r="D353" s="17"/>
@@ -6627,7 +6685,7 @@
       </c>
       <c r="I353" s="17"/>
     </row>
-    <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" s="17"/>
       <c r="C354" s="17"/>
       <c r="D354" s="17"/>
@@ -6640,7 +6698,7 @@
       </c>
       <c r="I354" s="17"/>
     </row>
-    <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B355" s="17"/>
       <c r="C355" s="17"/>
       <c r="D355" s="17"/>
@@ -6653,7 +6711,7 @@
       </c>
       <c r="I355" s="17"/>
     </row>
-    <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" s="17"/>
       <c r="C356" s="17"/>
       <c r="D356" s="17"/>
@@ -6666,7 +6724,7 @@
       </c>
       <c r="I356" s="17"/>
     </row>
-    <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B357" s="17"/>
       <c r="C357" s="17"/>
       <c r="D357" s="17"/>
@@ -6679,7 +6737,7 @@
       </c>
       <c r="I357" s="17"/>
     </row>
-    <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B358" s="17"/>
       <c r="C358" s="17"/>
       <c r="D358" s="17"/>
@@ -6692,7 +6750,7 @@
       </c>
       <c r="I358" s="17"/>
     </row>
-    <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B359" s="17"/>
       <c r="C359" s="17"/>
       <c r="D359" s="17"/>
@@ -6705,7 +6763,7 @@
       </c>
       <c r="I359" s="17"/>
     </row>
-    <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B360" s="17"/>
       <c r="C360" s="17"/>
       <c r="D360" s="17"/>
@@ -6718,7 +6776,7 @@
       </c>
       <c r="I360" s="17"/>
     </row>
-    <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B361" s="17"/>
       <c r="C361" s="17"/>
       <c r="D361" s="17"/>
@@ -6731,7 +6789,7 @@
       </c>
       <c r="I361" s="17"/>
     </row>
-    <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B362" s="17"/>
       <c r="C362" s="17"/>
       <c r="D362" s="17"/>
@@ -6744,7 +6802,7 @@
       </c>
       <c r="I362" s="17"/>
     </row>
-    <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B363" s="17"/>
       <c r="C363" s="17"/>
       <c r="D363" s="17"/>
@@ -6757,7 +6815,7 @@
       </c>
       <c r="I363" s="17"/>
     </row>
-    <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B364" s="17"/>
       <c r="C364" s="17"/>
       <c r="D364" s="17"/>
@@ -6770,7 +6828,7 @@
       </c>
       <c r="I364" s="17"/>
     </row>
-    <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B365" s="17"/>
       <c r="C365" s="17"/>
       <c r="D365" s="17"/>
@@ -6783,7 +6841,7 @@
       </c>
       <c r="I365" s="17"/>
     </row>
-    <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B366" s="17"/>
       <c r="C366" s="17"/>
       <c r="D366" s="17"/>
@@ -6796,7 +6854,7 @@
       </c>
       <c r="I366" s="17"/>
     </row>
-    <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B367" s="17"/>
       <c r="C367" s="17"/>
       <c r="D367" s="17"/>
@@ -6809,7 +6867,7 @@
       </c>
       <c r="I367" s="17"/>
     </row>
-    <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B368" s="17"/>
       <c r="C368" s="17"/>
       <c r="D368" s="17"/>
@@ -6822,7 +6880,7 @@
       </c>
       <c r="I368" s="17"/>
     </row>
-    <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B369" s="17"/>
       <c r="C369" s="17"/>
       <c r="D369" s="17"/>
@@ -6835,7 +6893,7 @@
       </c>
       <c r="I369" s="17"/>
     </row>
-    <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B370" s="17"/>
       <c r="C370" s="17"/>
       <c r="D370" s="17"/>
@@ -6848,7 +6906,7 @@
       </c>
       <c r="I370" s="17"/>
     </row>
-    <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B371" s="17"/>
       <c r="C371" s="17"/>
       <c r="D371" s="17"/>
@@ -6861,7 +6919,7 @@
       </c>
       <c r="I371" s="17"/>
     </row>
-    <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" s="17"/>
       <c r="C372" s="17"/>
       <c r="D372" s="17"/>
@@ -6874,7 +6932,7 @@
       </c>
       <c r="I372" s="17"/>
     </row>
-    <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B373" s="17"/>
       <c r="C373" s="17"/>
       <c r="D373" s="17"/>
@@ -6887,7 +6945,7 @@
       </c>
       <c r="I373" s="17"/>
     </row>
-    <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B374" s="17"/>
       <c r="C374" s="17"/>
       <c r="D374" s="17"/>
@@ -6900,7 +6958,7 @@
       </c>
       <c r="I374" s="17"/>
     </row>
-    <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B375" s="17"/>
       <c r="C375" s="17"/>
       <c r="D375" s="17"/>
@@ -6913,7 +6971,7 @@
       </c>
       <c r="I375" s="17"/>
     </row>
-    <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B376" s="17"/>
       <c r="C376" s="17"/>
       <c r="D376" s="17"/>
@@ -6926,7 +6984,7 @@
       </c>
       <c r="I376" s="17"/>
     </row>
-    <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B377" s="17"/>
       <c r="C377" s="17"/>
       <c r="D377" s="17"/>
@@ -6939,7 +6997,7 @@
       </c>
       <c r="I377" s="17"/>
     </row>
-    <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B378" s="17"/>
       <c r="C378" s="17"/>
       <c r="D378" s="17"/>
@@ -6952,7 +7010,7 @@
       </c>
       <c r="I378" s="17"/>
     </row>
-    <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B379" s="17"/>
       <c r="C379" s="17"/>
       <c r="D379" s="17"/>
@@ -6965,7 +7023,7 @@
       </c>
       <c r="I379" s="17"/>
     </row>
-    <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B380" s="17"/>
       <c r="C380" s="17"/>
       <c r="D380" s="17"/>
@@ -6978,7 +7036,7 @@
       </c>
       <c r="I380" s="17"/>
     </row>
-    <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B381" s="17"/>
       <c r="C381" s="17"/>
       <c r="D381" s="17"/>
@@ -6991,7 +7049,7 @@
       </c>
       <c r="I381" s="17"/>
     </row>
-    <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" s="17"/>
       <c r="C382" s="17"/>
       <c r="D382" s="17"/>
@@ -7004,7 +7062,7 @@
       </c>
       <c r="I382" s="17"/>
     </row>
-    <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B383" s="17"/>
       <c r="C383" s="17"/>
       <c r="D383" s="17"/>
@@ -7017,7 +7075,7 @@
       </c>
       <c r="I383" s="17"/>
     </row>
-    <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B384" s="17"/>
       <c r="C384" s="17"/>
       <c r="D384" s="17"/>
@@ -7030,7 +7088,7 @@
       </c>
       <c r="I384" s="17"/>
     </row>
-    <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B385" s="17"/>
       <c r="C385" s="17"/>
       <c r="D385" s="17"/>
@@ -7043,7 +7101,7 @@
       </c>
       <c r="I385" s="17"/>
     </row>
-    <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B386" s="17"/>
       <c r="C386" s="17"/>
       <c r="D386" s="17"/>
@@ -7056,7 +7114,7 @@
       </c>
       <c r="I386" s="17"/>
     </row>
-    <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B387" s="17"/>
       <c r="C387" s="17"/>
       <c r="D387" s="17"/>
@@ -7069,7 +7127,7 @@
       </c>
       <c r="I387" s="17"/>
     </row>
-    <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B388" s="17"/>
       <c r="C388" s="17"/>
       <c r="D388" s="17"/>
@@ -7082,7 +7140,7 @@
       </c>
       <c r="I388" s="17"/>
     </row>
-    <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B389" s="17"/>
       <c r="C389" s="17"/>
       <c r="D389" s="17"/>
@@ -7095,7 +7153,7 @@
       </c>
       <c r="I389" s="17"/>
     </row>
-    <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B390" s="17"/>
       <c r="C390" s="17"/>
       <c r="D390" s="17"/>
@@ -7108,7 +7166,7 @@
       </c>
       <c r="I390" s="17"/>
     </row>
-    <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B391" s="17"/>
       <c r="C391" s="17"/>
       <c r="D391" s="17"/>
@@ -7121,7 +7179,7 @@
       </c>
       <c r="I391" s="17"/>
     </row>
-    <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B392" s="17"/>
       <c r="C392" s="17"/>
       <c r="D392" s="17"/>
@@ -7134,7 +7192,7 @@
       </c>
       <c r="I392" s="17"/>
     </row>
-    <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B393" s="17"/>
       <c r="C393" s="17"/>
       <c r="D393" s="17"/>
@@ -7147,7 +7205,7 @@
       </c>
       <c r="I393" s="17"/>
     </row>
-    <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B394" s="17"/>
       <c r="C394" s="17"/>
       <c r="D394" s="17"/>
@@ -7160,7 +7218,7 @@
       </c>
       <c r="I394" s="17"/>
     </row>
-    <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B395" s="17"/>
       <c r="C395" s="17"/>
       <c r="D395" s="17"/>
@@ -7173,7 +7231,7 @@
       </c>
       <c r="I395" s="17"/>
     </row>
-    <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B396" s="17"/>
       <c r="C396" s="17"/>
       <c r="D396" s="17"/>
@@ -7186,7 +7244,7 @@
       </c>
       <c r="I396" s="17"/>
     </row>
-    <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B397" s="17"/>
       <c r="C397" s="17"/>
       <c r="D397" s="17"/>
@@ -7199,7 +7257,7 @@
       </c>
       <c r="I397" s="17"/>
     </row>
-    <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B398" s="17"/>
       <c r="C398" s="17"/>
       <c r="D398" s="17"/>
@@ -7212,7 +7270,7 @@
       </c>
       <c r="I398" s="17"/>
     </row>
-    <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B399" s="17"/>
       <c r="C399" s="17"/>
       <c r="D399" s="17"/>
@@ -7225,7 +7283,7 @@
       </c>
       <c r="I399" s="17"/>
     </row>
-    <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B400" s="17"/>
       <c r="C400" s="17"/>
       <c r="D400" s="17"/>
@@ -7238,7 +7296,7 @@
       </c>
       <c r="I400" s="17"/>
     </row>
-    <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B401" s="17"/>
       <c r="C401" s="17"/>
       <c r="D401" s="17"/>
@@ -7251,7 +7309,7 @@
       </c>
       <c r="I401" s="17"/>
     </row>
-    <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B402" s="17"/>
       <c r="C402" s="17"/>
       <c r="D402" s="17"/>
@@ -7264,7 +7322,7 @@
       </c>
       <c r="I402" s="17"/>
     </row>
-    <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B403" s="17"/>
       <c r="C403" s="17"/>
       <c r="D403" s="17"/>
@@ -7277,7 +7335,7 @@
       </c>
       <c r="I403" s="17"/>
     </row>
-    <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B404" s="17"/>
       <c r="C404" s="17"/>
       <c r="D404" s="17"/>
@@ -7290,7 +7348,7 @@
       </c>
       <c r="I404" s="17"/>
     </row>
-    <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B405" s="17"/>
       <c r="C405" s="17"/>
       <c r="D405" s="17"/>
@@ -7303,7 +7361,7 @@
       </c>
       <c r="I405" s="17"/>
     </row>
-    <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B406" s="17"/>
       <c r="C406" s="17"/>
       <c r="D406" s="17"/>
@@ -7316,7 +7374,7 @@
       </c>
       <c r="I406" s="17"/>
     </row>
-    <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B407" s="17"/>
       <c r="C407" s="17"/>
       <c r="D407" s="17"/>
@@ -7329,7 +7387,7 @@
       </c>
       <c r="I407" s="17"/>
     </row>
-    <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B408" s="17"/>
       <c r="C408" s="17"/>
       <c r="D408" s="17"/>
@@ -7342,7 +7400,7 @@
       </c>
       <c r="I408" s="17"/>
     </row>
-    <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B409" s="17"/>
       <c r="C409" s="17"/>
       <c r="D409" s="17"/>
@@ -7355,7 +7413,7 @@
       </c>
       <c r="I409" s="17"/>
     </row>
-    <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B410" s="17"/>
       <c r="C410" s="17"/>
       <c r="D410" s="17"/>
@@ -7368,7 +7426,7 @@
       </c>
       <c r="I410" s="17"/>
     </row>
-    <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B411" s="17"/>
       <c r="C411" s="17"/>
       <c r="D411" s="17"/>
@@ -7381,7 +7439,7 @@
       </c>
       <c r="I411" s="17"/>
     </row>
-    <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B412" s="17"/>
       <c r="C412" s="17"/>
       <c r="D412" s="17"/>
@@ -7394,7 +7452,7 @@
       </c>
       <c r="I412" s="17"/>
     </row>
-    <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B413" s="17"/>
       <c r="C413" s="17"/>
       <c r="D413" s="17"/>
@@ -7407,7 +7465,7 @@
       </c>
       <c r="I413" s="17"/>
     </row>
-    <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B414" s="17"/>
       <c r="C414" s="17"/>
       <c r="D414" s="17"/>
@@ -7420,7 +7478,7 @@
       </c>
       <c r="I414" s="17"/>
     </row>
-    <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B415" s="17"/>
       <c r="C415" s="17"/>
       <c r="D415" s="17"/>
@@ -7433,7 +7491,7 @@
       </c>
       <c r="I415" s="17"/>
     </row>
-    <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B416" s="17"/>
       <c r="C416" s="17"/>
       <c r="D416" s="17"/>
@@ -7446,7 +7504,7 @@
       </c>
       <c r="I416" s="17"/>
     </row>
-    <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B417" s="17"/>
       <c r="C417" s="17"/>
       <c r="D417" s="17"/>
@@ -7459,7 +7517,7 @@
       </c>
       <c r="I417" s="17"/>
     </row>
-    <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B418" s="17"/>
       <c r="C418" s="17"/>
       <c r="D418" s="17"/>
@@ -7472,7 +7530,7 @@
       </c>
       <c r="I418" s="17"/>
     </row>
-    <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B419" s="17"/>
       <c r="C419" s="17"/>
       <c r="D419" s="17"/>
@@ -7485,7 +7543,7 @@
       </c>
       <c r="I419" s="17"/>
     </row>
-    <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B420" s="17"/>
       <c r="C420" s="17"/>
       <c r="D420" s="17"/>
@@ -7498,7 +7556,7 @@
       </c>
       <c r="I420" s="17"/>
     </row>
-    <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B421" s="17"/>
       <c r="C421" s="17"/>
       <c r="D421" s="17"/>
@@ -7511,7 +7569,7 @@
       </c>
       <c r="I421" s="17"/>
     </row>
-    <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B422" s="17"/>
       <c r="C422" s="17"/>
       <c r="D422" s="17"/>
@@ -7524,7 +7582,7 @@
       </c>
       <c r="I422" s="17"/>
     </row>
-    <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B423" s="17"/>
       <c r="C423" s="17"/>
       <c r="D423" s="17"/>
@@ -7537,7 +7595,7 @@
       </c>
       <c r="I423" s="17"/>
     </row>
-    <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B424" s="17"/>
       <c r="C424" s="17"/>
       <c r="D424" s="17"/>
@@ -7550,7 +7608,7 @@
       </c>
       <c r="I424" s="17"/>
     </row>
-    <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B425" s="17"/>
       <c r="C425" s="17"/>
       <c r="D425" s="17"/>
@@ -7563,7 +7621,7 @@
       </c>
       <c r="I425" s="17"/>
     </row>
-    <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B426" s="17"/>
       <c r="C426" s="17"/>
       <c r="D426" s="17"/>
@@ -7576,7 +7634,7 @@
       </c>
       <c r="I426" s="17"/>
     </row>
-    <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B427" s="17"/>
       <c r="C427" s="17"/>
       <c r="D427" s="17"/>
@@ -7589,7 +7647,7 @@
       </c>
       <c r="I427" s="17"/>
     </row>
-    <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B428" s="17"/>
       <c r="C428" s="17"/>
       <c r="D428" s="17"/>
@@ -7602,7 +7660,7 @@
       </c>
       <c r="I428" s="17"/>
     </row>
-    <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B429" s="17"/>
       <c r="C429" s="17"/>
       <c r="D429" s="17"/>
@@ -7615,7 +7673,7 @@
       </c>
       <c r="I429" s="17"/>
     </row>
-    <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B430" s="17"/>
       <c r="C430" s="17"/>
       <c r="D430" s="17"/>
@@ -7628,7 +7686,7 @@
       </c>
       <c r="I430" s="17"/>
     </row>
-    <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B431" s="17"/>
       <c r="C431" s="17"/>
       <c r="D431" s="17"/>
@@ -7641,7 +7699,7 @@
       </c>
       <c r="I431" s="17"/>
     </row>
-    <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B432" s="17"/>
       <c r="C432" s="17"/>
       <c r="D432" s="17"/>
@@ -7654,7 +7712,7 @@
       </c>
       <c r="I432" s="17"/>
     </row>
-    <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B433" s="17"/>
       <c r="C433" s="17"/>
       <c r="D433" s="17"/>
@@ -7667,7 +7725,7 @@
       </c>
       <c r="I433" s="17"/>
     </row>
-    <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B434" s="17"/>
       <c r="C434" s="17"/>
       <c r="D434" s="17"/>
@@ -7680,7 +7738,7 @@
       </c>
       <c r="I434" s="17"/>
     </row>
-    <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B435" s="17"/>
       <c r="C435" s="17"/>
       <c r="D435" s="17"/>
@@ -7693,7 +7751,7 @@
       </c>
       <c r="I435" s="17"/>
     </row>
-    <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B436" s="17"/>
       <c r="C436" s="17"/>
       <c r="D436" s="17"/>
@@ -7706,7 +7764,7 @@
       </c>
       <c r="I436" s="17"/>
     </row>
-    <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B437" s="17"/>
       <c r="C437" s="17"/>
       <c r="D437" s="17"/>
@@ -7719,7 +7777,7 @@
       </c>
       <c r="I437" s="17"/>
     </row>
-    <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B438" s="17"/>
       <c r="C438" s="17"/>
       <c r="D438" s="17"/>
@@ -7732,7 +7790,7 @@
       </c>
       <c r="I438" s="17"/>
     </row>
-    <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B439" s="17"/>
       <c r="C439" s="17"/>
       <c r="D439" s="17"/>
@@ -7745,7 +7803,7 @@
       </c>
       <c r="I439" s="17"/>
     </row>
-    <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B440" s="17"/>
       <c r="C440" s="17"/>
       <c r="D440" s="17"/>
@@ -7758,7 +7816,7 @@
       </c>
       <c r="I440" s="17"/>
     </row>
-    <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B441" s="17"/>
       <c r="C441" s="17"/>
       <c r="D441" s="17"/>
@@ -7771,7 +7829,7 @@
       </c>
       <c r="I441" s="17"/>
     </row>
-    <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B442" s="17"/>
       <c r="C442" s="17"/>
       <c r="D442" s="17"/>
@@ -7784,7 +7842,7 @@
       </c>
       <c r="I442" s="17"/>
     </row>
-    <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B443" s="17"/>
       <c r="C443" s="17"/>
       <c r="D443" s="17"/>
@@ -7797,7 +7855,7 @@
       </c>
       <c r="I443" s="17"/>
     </row>
-    <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B444" s="17"/>
       <c r="C444" s="17"/>
       <c r="D444" s="17"/>
@@ -7810,7 +7868,7 @@
       </c>
       <c r="I444" s="17"/>
     </row>
-    <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B445" s="17"/>
       <c r="C445" s="17"/>
       <c r="D445" s="17"/>
@@ -7823,7 +7881,7 @@
       </c>
       <c r="I445" s="17"/>
     </row>
-    <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B446" s="17"/>
       <c r="C446" s="17"/>
       <c r="D446" s="17"/>
@@ -7836,7 +7894,7 @@
       </c>
       <c r="I446" s="17"/>
     </row>
-    <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B447" s="17"/>
       <c r="C447" s="17"/>
       <c r="D447" s="17"/>
@@ -7849,7 +7907,7 @@
       </c>
       <c r="I447" s="17"/>
     </row>
-    <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B448" s="17"/>
       <c r="C448" s="17"/>
       <c r="D448" s="17"/>
@@ -7862,7 +7920,7 @@
       </c>
       <c r="I448" s="17"/>
     </row>
-    <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B449" s="17"/>
       <c r="C449" s="17"/>
       <c r="D449" s="17"/>
@@ -7875,7 +7933,7 @@
       </c>
       <c r="I449" s="17"/>
     </row>
-    <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B450" s="17"/>
       <c r="C450" s="17"/>
       <c r="D450" s="17"/>
@@ -7888,7 +7946,7 @@
       </c>
       <c r="I450" s="17"/>
     </row>
-    <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B451" s="17"/>
       <c r="C451" s="17"/>
       <c r="D451" s="17"/>
@@ -7901,7 +7959,7 @@
       </c>
       <c r="I451" s="17"/>
     </row>
-    <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B452" s="17"/>
       <c r="C452" s="17"/>
       <c r="D452" s="17"/>
@@ -7914,7 +7972,7 @@
       </c>
       <c r="I452" s="17"/>
     </row>
-    <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B453" s="17"/>
       <c r="C453" s="17"/>
       <c r="D453" s="17"/>
@@ -7927,7 +7985,7 @@
       </c>
       <c r="I453" s="17"/>
     </row>
-    <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B454" s="17"/>
       <c r="C454" s="17"/>
       <c r="D454" s="17"/>
@@ -7940,7 +7998,7 @@
       </c>
       <c r="I454" s="17"/>
     </row>
-    <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B455" s="17"/>
       <c r="C455" s="17"/>
       <c r="D455" s="17"/>
@@ -7953,7 +8011,7 @@
       </c>
       <c r="I455" s="17"/>
     </row>
-    <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B456" s="17"/>
       <c r="C456" s="17"/>
       <c r="D456" s="17"/>
@@ -7966,7 +8024,7 @@
       </c>
       <c r="I456" s="17"/>
     </row>
-    <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B457" s="17"/>
       <c r="C457" s="17"/>
       <c r="D457" s="17"/>
@@ -7979,7 +8037,7 @@
       </c>
       <c r="I457" s="17"/>
     </row>
-    <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B458" s="17"/>
       <c r="C458" s="17"/>
       <c r="D458" s="17"/>
@@ -7992,7 +8050,7 @@
       </c>
       <c r="I458" s="17"/>
     </row>
-    <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B459" s="17"/>
       <c r="C459" s="17"/>
       <c r="D459" s="17"/>
@@ -8005,7 +8063,7 @@
       </c>
       <c r="I459" s="17"/>
     </row>
-    <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B460" s="17"/>
       <c r="C460" s="17"/>
       <c r="D460" s="17"/>
@@ -8018,7 +8076,7 @@
       </c>
       <c r="I460" s="17"/>
     </row>
-    <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B461" s="17"/>
       <c r="C461" s="17"/>
       <c r="D461" s="17"/>
@@ -8031,7 +8089,7 @@
       </c>
       <c r="I461" s="17"/>
     </row>
-    <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B462" s="17"/>
       <c r="C462" s="17"/>
       <c r="D462" s="17"/>
@@ -8044,7 +8102,7 @@
       </c>
       <c r="I462" s="17"/>
     </row>
-    <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B463" s="17"/>
       <c r="C463" s="17"/>
       <c r="D463" s="17"/>
@@ -8057,7 +8115,7 @@
       </c>
       <c r="I463" s="17"/>
     </row>
-    <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B464" s="17"/>
       <c r="C464" s="17"/>
       <c r="D464" s="17"/>
@@ -8070,7 +8128,7 @@
       </c>
       <c r="I464" s="17"/>
     </row>
-    <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B465" s="17"/>
       <c r="C465" s="17"/>
       <c r="D465" s="17"/>
@@ -8083,7 +8141,7 @@
       </c>
       <c r="I465" s="17"/>
     </row>
-    <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B466" s="17"/>
       <c r="C466" s="17"/>
       <c r="D466" s="17"/>
@@ -8096,7 +8154,7 @@
       </c>
       <c r="I466" s="17"/>
     </row>
-    <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B467" s="17"/>
       <c r="C467" s="17"/>
       <c r="D467" s="17"/>
@@ -8109,7 +8167,7 @@
       </c>
       <c r="I467" s="17"/>
     </row>
-    <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B468" s="17"/>
       <c r="C468" s="17"/>
       <c r="D468" s="17"/>
@@ -8122,7 +8180,7 @@
       </c>
       <c r="I468" s="17"/>
     </row>
-    <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B469" s="17"/>
       <c r="C469" s="17"/>
       <c r="D469" s="17"/>
@@ -8135,7 +8193,7 @@
       </c>
       <c r="I469" s="17"/>
     </row>
-    <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B470" s="17"/>
       <c r="C470" s="17"/>
       <c r="D470" s="17"/>
@@ -8148,7 +8206,7 @@
       </c>
       <c r="I470" s="17"/>
     </row>
-    <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B471" s="17"/>
       <c r="C471" s="17"/>
       <c r="D471" s="17"/>
@@ -8161,7 +8219,7 @@
       </c>
       <c r="I471" s="17"/>
     </row>
-    <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B472" s="17"/>
       <c r="C472" s="17"/>
       <c r="D472" s="17"/>
@@ -8174,7 +8232,7 @@
       </c>
       <c r="I472" s="17"/>
     </row>
-    <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B473" s="17"/>
       <c r="C473" s="17"/>
       <c r="D473" s="17"/>
@@ -8187,7 +8245,7 @@
       </c>
       <c r="I473" s="17"/>
     </row>
-    <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B474" s="17"/>
       <c r="C474" s="17"/>
       <c r="D474" s="17"/>
@@ -8200,7 +8258,7 @@
       </c>
       <c r="I474" s="17"/>
     </row>
-    <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B475" s="17"/>
       <c r="C475" s="17"/>
       <c r="D475" s="17"/>
@@ -8213,7 +8271,7 @@
       </c>
       <c r="I475" s="17"/>
     </row>
-    <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B476" s="17"/>
       <c r="C476" s="17"/>
       <c r="D476" s="17"/>
@@ -8226,7 +8284,7 @@
       </c>
       <c r="I476" s="17"/>
     </row>
-    <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B477" s="17"/>
       <c r="C477" s="17"/>
       <c r="D477" s="17"/>
@@ -8239,7 +8297,7 @@
       </c>
       <c r="I477" s="17"/>
     </row>
-    <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B478" s="17"/>
       <c r="C478" s="17"/>
       <c r="D478" s="17"/>
@@ -8252,7 +8310,7 @@
       </c>
       <c r="I478" s="17"/>
     </row>
-    <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B479" s="17"/>
       <c r="C479" s="17"/>
       <c r="D479" s="17"/>
@@ -8265,7 +8323,7 @@
       </c>
       <c r="I479" s="17"/>
     </row>
-    <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B480" s="17"/>
       <c r="C480" s="17"/>
       <c r="D480" s="17"/>
@@ -8278,7 +8336,7 @@
       </c>
       <c r="I480" s="17"/>
     </row>
-    <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B481" s="17"/>
       <c r="C481" s="17"/>
       <c r="D481" s="17"/>
@@ -8291,7 +8349,7 @@
       </c>
       <c r="I481" s="17"/>
     </row>
-    <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B482" s="17"/>
       <c r="C482" s="17"/>
       <c r="D482" s="17"/>
@@ -8304,7 +8362,7 @@
       </c>
       <c r="I482" s="17"/>
     </row>
-    <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B483" s="17"/>
       <c r="C483" s="17"/>
       <c r="D483" s="17"/>
@@ -8317,7 +8375,7 @@
       </c>
       <c r="I483" s="17"/>
     </row>
-    <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B484" s="17"/>
       <c r="C484" s="17"/>
       <c r="D484" s="17"/>
@@ -8330,7 +8388,7 @@
       </c>
       <c r="I484" s="17"/>
     </row>
-    <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B485" s="17"/>
       <c r="C485" s="17"/>
       <c r="D485" s="17"/>
@@ -8343,7 +8401,7 @@
       </c>
       <c r="I485" s="17"/>
     </row>
-    <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B486" s="17"/>
       <c r="C486" s="17"/>
       <c r="D486" s="17"/>
@@ -8356,7 +8414,7 @@
       </c>
       <c r="I486" s="17"/>
     </row>
-    <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B487" s="17"/>
       <c r="C487" s="17"/>
       <c r="D487" s="17"/>
@@ -8369,7 +8427,7 @@
       </c>
       <c r="I487" s="17"/>
     </row>
-    <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B488" s="17"/>
       <c r="C488" s="17"/>
       <c r="D488" s="17"/>
@@ -8382,7 +8440,7 @@
       </c>
       <c r="I488" s="17"/>
     </row>
-    <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B489" s="17"/>
       <c r="C489" s="17"/>
       <c r="D489" s="17"/>
@@ -8395,7 +8453,7 @@
       </c>
       <c r="I489" s="17"/>
     </row>
-    <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B490" s="17"/>
       <c r="C490" s="17"/>
       <c r="D490" s="17"/>
@@ -8408,7 +8466,7 @@
       </c>
       <c r="I490" s="17"/>
     </row>
-    <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B491" s="17"/>
       <c r="C491" s="17"/>
       <c r="D491" s="17"/>
@@ -8421,7 +8479,7 @@
       </c>
       <c r="I491" s="17"/>
     </row>
-    <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B492" s="17"/>
       <c r="C492" s="17"/>
       <c r="D492" s="17"/>
@@ -8434,7 +8492,7 @@
       </c>
       <c r="I492" s="17"/>
     </row>
-    <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B493" s="17"/>
       <c r="C493" s="17"/>
       <c r="D493" s="17"/>
@@ -8447,7 +8505,7 @@
       </c>
       <c r="I493" s="17"/>
     </row>
-    <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B494" s="17"/>
       <c r="C494" s="17"/>
       <c r="D494" s="17"/>
@@ -8460,7 +8518,7 @@
       </c>
       <c r="I494" s="17"/>
     </row>
-    <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B495" s="17"/>
       <c r="C495" s="17"/>
       <c r="D495" s="17"/>
@@ -8473,7 +8531,7 @@
       </c>
       <c r="I495" s="17"/>
     </row>
-    <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B496" s="17"/>
       <c r="C496" s="17"/>
       <c r="D496" s="17"/>
@@ -8486,7 +8544,7 @@
       </c>
       <c r="I496" s="17"/>
     </row>
-    <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B497" s="17"/>
       <c r="C497" s="17"/>
       <c r="D497" s="17"/>
@@ -8499,7 +8557,7 @@
       </c>
       <c r="I497" s="17"/>
     </row>
-    <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B498" s="17"/>
       <c r="C498" s="17"/>
       <c r="D498" s="17"/>
@@ -8512,7 +8570,7 @@
       </c>
       <c r="I498" s="17"/>
     </row>
-    <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B499" s="17"/>
       <c r="C499" s="17"/>
       <c r="D499" s="17"/>
@@ -8525,7 +8583,7 @@
       </c>
       <c r="I499" s="17"/>
     </row>
-    <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B500" s="17"/>
       <c r="C500" s="17"/>
       <c r="D500" s="17"/>
@@ -8538,7 +8596,7 @@
       </c>
       <c r="I500" s="17"/>
     </row>
-    <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B501" s="17"/>
       <c r="C501" s="17"/>
       <c r="D501" s="17"/>
@@ -8551,7 +8609,7 @@
       </c>
       <c r="I501" s="17"/>
     </row>
-    <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B502" s="17"/>
       <c r="C502" s="17"/>
       <c r="D502" s="17"/>
@@ -8564,7 +8622,7 @@
       </c>
       <c r="I502" s="17"/>
     </row>
-    <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B503" s="17"/>
       <c r="C503" s="17"/>
       <c r="D503" s="17"/>
@@ -8577,7 +8635,7 @@
       </c>
       <c r="I503" s="17"/>
     </row>
-    <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B504" s="17"/>
       <c r="C504" s="17"/>
       <c r="D504" s="17"/>
@@ -8590,7 +8648,7 @@
       </c>
       <c r="I504" s="17"/>
     </row>
-    <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B505" s="17"/>
       <c r="C505" s="17"/>
       <c r="D505" s="17"/>
@@ -8603,7 +8661,7 @@
       </c>
       <c r="I505" s="17"/>
     </row>
-    <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B506" s="17"/>
       <c r="C506" s="17"/>
       <c r="D506" s="17"/>
@@ -8616,7 +8674,7 @@
       </c>
       <c r="I506" s="17"/>
     </row>
-    <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B507" s="17"/>
       <c r="C507" s="17"/>
       <c r="D507" s="17"/>
@@ -8629,7 +8687,7 @@
       </c>
       <c r="I507" s="17"/>
     </row>
-    <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B508" s="17"/>
       <c r="C508" s="17"/>
       <c r="D508" s="17"/>
@@ -8642,7 +8700,7 @@
       </c>
       <c r="I508" s="17"/>
     </row>
-    <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B509" s="17"/>
       <c r="C509" s="17"/>
       <c r="D509" s="17"/>
@@ -8655,7 +8713,7 @@
       </c>
       <c r="I509" s="17"/>
     </row>
-    <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B510" s="17"/>
       <c r="C510" s="17"/>
       <c r="D510" s="17"/>
@@ -8668,7 +8726,7 @@
       </c>
       <c r="I510" s="17"/>
     </row>
-    <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B511" s="17"/>
       <c r="C511" s="17"/>
       <c r="D511" s="17"/>
@@ -8681,7 +8739,7 @@
       </c>
       <c r="I511" s="17"/>
     </row>
-    <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B512" s="17"/>
       <c r="C512" s="17"/>
       <c r="D512" s="17"/>
@@ -8694,7 +8752,7 @@
       </c>
       <c r="I512" s="17"/>
     </row>
-    <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B513" s="17"/>
       <c r="C513" s="17"/>
       <c r="D513" s="17"/>
@@ -8707,7 +8765,7 @@
       </c>
       <c r="I513" s="17"/>
     </row>
-    <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B514" s="17"/>
       <c r="C514" s="17"/>
       <c r="D514" s="17"/>
@@ -8720,7 +8778,7 @@
       </c>
       <c r="I514" s="17"/>
     </row>
-    <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B515" s="17"/>
       <c r="C515" s="17"/>
       <c r="D515" s="17"/>
@@ -8733,7 +8791,7 @@
       </c>
       <c r="I515" s="17"/>
     </row>
-    <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B516" s="17"/>
       <c r="C516" s="17"/>
       <c r="D516" s="17"/>
@@ -8746,7 +8804,7 @@
       </c>
       <c r="I516" s="17"/>
     </row>
-    <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B517" s="17"/>
       <c r="C517" s="17"/>
       <c r="D517" s="17"/>
@@ -8759,7 +8817,7 @@
       </c>
       <c r="I517" s="17"/>
     </row>
-    <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B518" s="17"/>
       <c r="C518" s="17"/>
       <c r="D518" s="17"/>
@@ -8772,7 +8830,7 @@
       </c>
       <c r="I518" s="17"/>
     </row>
-    <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B519" s="17"/>
       <c r="C519" s="17"/>
       <c r="D519" s="17"/>
@@ -8785,7 +8843,7 @@
       </c>
       <c r="I519" s="17"/>
     </row>
-    <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B520" s="17"/>
       <c r="C520" s="17"/>
       <c r="D520" s="17"/>
@@ -8798,7 +8856,7 @@
       </c>
       <c r="I520" s="17"/>
     </row>
-    <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B521" s="17"/>
       <c r="C521" s="17"/>
       <c r="D521" s="17"/>
@@ -8811,7 +8869,7 @@
       </c>
       <c r="I521" s="17"/>
     </row>
-    <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B522" s="17"/>
       <c r="C522" s="17"/>
       <c r="D522" s="17"/>
@@ -8824,7 +8882,7 @@
       </c>
       <c r="I522" s="17"/>
     </row>
-    <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B523" s="17"/>
       <c r="C523" s="17"/>
       <c r="D523" s="17"/>
@@ -8837,7 +8895,7 @@
       </c>
       <c r="I523" s="17"/>
     </row>
-    <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B524" s="17"/>
       <c r="C524" s="17"/>
       <c r="D524" s="17"/>
@@ -8850,7 +8908,7 @@
       </c>
       <c r="I524" s="17"/>
     </row>
-    <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B525" s="17"/>
       <c r="C525" s="17"/>
       <c r="D525" s="17"/>
@@ -8863,7 +8921,7 @@
       </c>
       <c r="I525" s="17"/>
     </row>
-    <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B526" s="17"/>
       <c r="C526" s="17"/>
       <c r="D526" s="17"/>
@@ -8876,7 +8934,7 @@
       </c>
       <c r="I526" s="17"/>
     </row>
-    <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B527" s="17"/>
       <c r="C527" s="17"/>
       <c r="D527" s="17"/>
@@ -8889,7 +8947,7 @@
       </c>
       <c r="I527" s="17"/>
     </row>
-    <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B528" s="17"/>
       <c r="C528" s="17"/>
       <c r="D528" s="17"/>
@@ -8902,7 +8960,7 @@
       </c>
       <c r="I528" s="17"/>
     </row>
-    <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B529" s="17"/>
       <c r="C529" s="17"/>
       <c r="D529" s="17"/>
@@ -8915,7 +8973,7 @@
       </c>
       <c r="I529" s="17"/>
     </row>
-    <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B530" s="17"/>
       <c r="C530" s="17"/>
       <c r="D530" s="17"/>
@@ -8928,7 +8986,7 @@
       </c>
       <c r="I530" s="17"/>
     </row>
-    <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B531" s="17"/>
       <c r="C531" s="17"/>
       <c r="D531" s="17"/>
@@ -8941,7 +8999,7 @@
       </c>
       <c r="I531" s="17"/>
     </row>
-    <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B532" s="17"/>
       <c r="C532" s="17"/>
       <c r="D532" s="17"/>
@@ -8954,7 +9012,7 @@
       </c>
       <c r="I532" s="17"/>
     </row>
-    <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B533" s="17"/>
       <c r="C533" s="17"/>
       <c r="D533" s="17"/>
@@ -8967,7 +9025,7 @@
       </c>
       <c r="I533" s="17"/>
     </row>
-    <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B534" s="17"/>
       <c r="C534" s="17"/>
       <c r="D534" s="17"/>
@@ -8980,7 +9038,7 @@
       </c>
       <c r="I534" s="17"/>
     </row>
-    <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B535" s="17"/>
       <c r="C535" s="17"/>
       <c r="D535" s="17"/>
@@ -8993,7 +9051,7 @@
       </c>
       <c r="I535" s="17"/>
     </row>
-    <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B536" s="17"/>
       <c r="C536" s="17"/>
       <c r="D536" s="17"/>
@@ -9006,7 +9064,7 @@
       </c>
       <c r="I536" s="17"/>
     </row>
-    <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B537" s="17"/>
       <c r="C537" s="17"/>
       <c r="D537" s="17"/>
@@ -9019,7 +9077,7 @@
       </c>
       <c r="I537" s="17"/>
     </row>
-    <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B538" s="17"/>
       <c r="C538" s="17"/>
       <c r="D538" s="17"/>
@@ -9032,7 +9090,7 @@
       </c>
       <c r="I538" s="17"/>
     </row>
-    <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B539" s="17"/>
       <c r="C539" s="17"/>
       <c r="D539" s="17"/>
@@ -9045,7 +9103,7 @@
       </c>
       <c r="I539" s="17"/>
     </row>
-    <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B540" s="17"/>
       <c r="C540" s="17"/>
       <c r="D540" s="17"/>
@@ -9058,7 +9116,7 @@
       </c>
       <c r="I540" s="17"/>
     </row>
-    <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B541" s="17"/>
       <c r="C541" s="17"/>
       <c r="D541" s="17"/>
@@ -9071,7 +9129,7 @@
       </c>
       <c r="I541" s="17"/>
     </row>
-    <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B542" s="17"/>
       <c r="C542" s="17"/>
       <c r="D542" s="17"/>
@@ -9084,7 +9142,7 @@
       </c>
       <c r="I542" s="17"/>
     </row>
-    <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B543" s="17"/>
       <c r="C543" s="17"/>
       <c r="D543" s="17"/>
@@ -9097,7 +9155,7 @@
       </c>
       <c r="I543" s="17"/>
     </row>
-    <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B544" s="17"/>
       <c r="C544" s="17"/>
       <c r="D544" s="17"/>
@@ -9110,7 +9168,7 @@
       </c>
       <c r="I544" s="17"/>
     </row>
-    <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B545" s="17"/>
       <c r="C545" s="17"/>
       <c r="D545" s="17"/>
@@ -9123,7 +9181,7 @@
       </c>
       <c r="I545" s="17"/>
     </row>
-    <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B546" s="17"/>
       <c r="C546" s="17"/>
       <c r="D546" s="17"/>
@@ -9136,7 +9194,7 @@
       </c>
       <c r="I546" s="17"/>
     </row>
-    <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B547" s="17"/>
       <c r="C547" s="17"/>
       <c r="D547" s="17"/>
@@ -9149,7 +9207,7 @@
       </c>
       <c r="I547" s="17"/>
     </row>
-    <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B548" s="17"/>
       <c r="C548" s="17"/>
       <c r="D548" s="17"/>
@@ -9162,7 +9220,7 @@
       </c>
       <c r="I548" s="17"/>
     </row>
-    <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B549" s="17"/>
       <c r="C549" s="17"/>
       <c r="D549" s="17"/>
@@ -9175,7 +9233,7 @@
       </c>
       <c r="I549" s="17"/>
     </row>
-    <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B550" s="17"/>
       <c r="C550" s="17"/>
       <c r="D550" s="17"/>
@@ -9188,7 +9246,7 @@
       </c>
       <c r="I550" s="17"/>
     </row>
-    <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B551" s="17"/>
       <c r="C551" s="17"/>
       <c r="D551" s="17"/>
@@ -9201,7 +9259,7 @@
       </c>
       <c r="I551" s="17"/>
     </row>
-    <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B552" s="17"/>
       <c r="C552" s="17"/>
       <c r="D552" s="17"/>
@@ -9214,7 +9272,7 @@
       </c>
       <c r="I552" s="17"/>
     </row>
-    <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B553" s="17"/>
       <c r="C553" s="17"/>
       <c r="D553" s="17"/>
@@ -9224,7 +9282,7 @@
       <c r="H553" s="20"/>
       <c r="I553" s="17"/>
     </row>
-    <row r="554" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B554" s="17"/>
       <c r="C554" s="17"/>
       <c r="D554" s="17"/>
@@ -9234,7 +9292,7 @@
       <c r="H554" s="20"/>
       <c r="I554" s="17"/>
     </row>
-    <row r="555" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B555" s="17"/>
       <c r="C555" s="17"/>
       <c r="D555" s="17"/>
@@ -9244,7 +9302,7 @@
       <c r="H555" s="20"/>
       <c r="I555" s="17"/>
     </row>
-    <row r="556" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B556" s="17"/>
       <c r="C556" s="17"/>
       <c r="D556" s="17"/>
@@ -9254,7 +9312,7 @@
       <c r="H556" s="20"/>
       <c r="I556" s="17"/>
     </row>
-    <row r="557" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B557" s="17"/>
       <c r="C557" s="17"/>
       <c r="D557" s="17"/>
@@ -9264,7 +9322,7 @@
       <c r="H557" s="20"/>
       <c r="I557" s="17"/>
     </row>
-    <row r="558" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B558" s="17"/>
       <c r="C558" s="17"/>
       <c r="D558" s="17"/>
@@ -9274,7 +9332,7 @@
       <c r="H558" s="20"/>
       <c r="I558" s="17"/>
     </row>
-    <row r="559" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B559" s="17"/>
       <c r="C559" s="17"/>
       <c r="D559" s="17"/>
@@ -9284,7 +9342,7 @@
       <c r="H559" s="20"/>
       <c r="I559" s="17"/>
     </row>
-    <row r="560" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B560" s="17"/>
       <c r="C560" s="17"/>
       <c r="D560" s="17"/>
@@ -9294,7 +9352,7 @@
       <c r="H560" s="20"/>
       <c r="I560" s="17"/>
     </row>
-    <row r="561" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B561" s="17"/>
       <c r="C561" s="17"/>
       <c r="D561" s="17"/>
@@ -9304,7 +9362,7 @@
       <c r="H561" s="20"/>
       <c r="I561" s="17"/>
     </row>
-    <row r="562" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B562" s="17"/>
       <c r="C562" s="17"/>
       <c r="D562" s="17"/>
@@ -9314,7 +9372,7 @@
       <c r="H562" s="20"/>
       <c r="I562" s="17"/>
     </row>
-    <row r="563" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B563" s="17"/>
       <c r="C563" s="17"/>
       <c r="D563" s="17"/>
@@ -9366,16 +9424,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="15.609375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="25.27734375" style="26" customWidth="1"/>
-    <col min="5" max="16384" width="8.71875" style="26"/>
+    <col min="1" max="1" width="32.81640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="25.26953125" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>50</v>
       </c>
@@ -9389,7 +9447,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>53</v>
       </c>
@@ -9403,7 +9461,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>58</v>
       </c>
@@ -9417,7 +9475,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>58</v>
       </c>
@@ -9431,7 +9489,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>58</v>
       </c>
@@ -9445,7 +9503,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>56</v>
       </c>
@@ -9459,7 +9517,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>56</v>
       </c>
@@ -9473,7 +9531,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>56</v>
       </c>
@@ -9487,7 +9545,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>56</v>
       </c>
@@ -9501,7 +9559,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>63</v>
       </c>
@@ -9522,27 +9580,226 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2808761C-DB74-40A1-A14C-7D3D09C06A44}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="54.6328125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="19.7265625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" style="26" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="19.08984375" style="26" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45601</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45618</v>
+      </c>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45601</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45605</v>
+      </c>
+      <c r="D3" s="29"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45605</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45610</v>
+      </c>
+      <c r="D4" s="29"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45610</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45615</v>
+      </c>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45602</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45618</v>
+      </c>
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45606</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45611</v>
+      </c>
+      <c r="D7" s="29"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="28">
+        <v>45615</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45618</v>
+      </c>
+      <c r="D8" s="29"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="28">
+        <v>45611</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45620</v>
+      </c>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="28">
+        <v>45614</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45618</v>
+      </c>
+      <c r="D10" s="29"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45619</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45621</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="28">
+        <v>45619</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45622</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="28">
+        <v>45619</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45621</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="28">
+        <v>45630</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="28">
+        <v>45630</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45630</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor theme="7" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.71875" style="11" customWidth="1"/>
-    <col min="2" max="3" width="18.44140625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="6.71875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="11" customWidth="1"/>
+    <col min="2" max="3" width="18.453125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="12" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="15" t="s">
         <v>1</v>
@@ -9550,13 +9807,13 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="21" t="s">
         <v>2</v>
@@ -9566,7 +9823,7 @@
       </c>
       <c r="D4" s="14"/>
     </row>
-    <row r="5" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="21" t="s">
         <v>12</v>
@@ -9576,7 +9833,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="21" t="s">
         <v>13</v>
@@ -9586,7 +9843,7 @@
       </c>
       <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="21" t="s">
         <v>14</v>
@@ -9596,7 +9853,7 @@
       </c>
       <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="21" t="s">
         <v>15</v>
@@ -9606,7 +9863,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="9" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="21" t="s">
         <v>16</v>
@@ -9616,7 +9873,7 @@
       </c>
       <c r="D9" s="12"/>
     </row>
-    <row r="10" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="21" t="s">
         <v>17</v>
@@ -9626,7 +9883,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21" t="s">
@@ -9634,109 +9891,109 @@
       </c>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21"/>
       <c r="C12" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
       <c r="C13" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="21"/>
       <c r="C14" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="21"/>
       <c r="C15" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="21"/>
       <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
       <c r="C19" s="21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="21"/>
       <c r="C20" s="21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="21"/>
       <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="21"/>
       <c r="C22" s="21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="21"/>
       <c r="C23" s="21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="21"/>
       <c r="C24" s="21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="21"/>
       <c r="C25" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
       <c r="C26" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="21"/>
       <c r="C27" s="21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="21"/>
       <c r="C28" s="21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="21"/>
       <c r="C29" s="21" t="s">
         <v>42</v>
@@ -9759,23 +10016,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10091,22 +10337,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10133,9 +10386,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Iteration_1/project_tracker.xlsx
+++ b/Iteration_1/project_tracker.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63A823F-04F1-45EA-8C02-5DA6C448FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AEFD75-5F4E-4298-89F4-53E56A2DEA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="116">
   <si>
     <t>Category</t>
   </si>
@@ -377,6 +377,15 @@
   </si>
   <si>
     <t>Finalize leaderboard and matchmaking logic</t>
+  </si>
+  <si>
+    <t>P2 Planning</t>
+  </si>
+  <si>
+    <t>Complete feedback for Delta and Echo team</t>
+  </si>
+  <si>
+    <t>Complete letter and submit P2</t>
   </si>
 </sst>
 </file>
@@ -9423,7 +9432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.81640625" style="26" customWidth="1"/>
@@ -9573,6 +9582,20 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45604</v>
+      </c>
+      <c r="D11" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -9581,7 +9604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2808761C-DB74-40A1-A14C-7D3D09C06A44}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.6328125" style="26" customWidth="1"/>
@@ -9659,34 +9682,34 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="28">
-        <v>45602</v>
+        <v>45604</v>
       </c>
       <c r="C6" s="28">
-        <v>45618</v>
+        <v>45608</v>
       </c>
       <c r="D6" s="29"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B7" s="28">
-        <v>45606</v>
+        <v>45608</v>
       </c>
       <c r="C7" s="28">
-        <v>45611</v>
+        <v>45609</v>
       </c>
       <c r="D7" s="29"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" s="28">
-        <v>45615</v>
+        <v>45602</v>
       </c>
       <c r="C8" s="28">
         <v>45618</v>
@@ -9695,22 +9718,22 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B9" s="28">
+        <v>45606</v>
+      </c>
+      <c r="C9" s="28">
         <v>45611</v>
-      </c>
-      <c r="C9" s="28">
-        <v>45620</v>
       </c>
       <c r="D9" s="29"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B10" s="28">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C10" s="28">
         <v>45618</v>
@@ -9719,29 +9742,29 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B11" s="28">
-        <v>45619</v>
+        <v>45611</v>
       </c>
       <c r="C11" s="28">
-        <v>45621</v>
+        <v>45620</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B12" s="28">
-        <v>45619</v>
+        <v>45614</v>
       </c>
       <c r="C12" s="28">
-        <v>45622</v>
+        <v>45618</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="28">
         <v>45619</v>
@@ -9752,23 +9775,45 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="28">
-        <v>45630</v>
+        <v>45619</v>
       </c>
       <c r="C14" s="28">
-        <v>45630</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="28">
+        <v>45619</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45621</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="28">
+        <v>45630</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B17" s="28">
         <v>45630</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C17" s="28">
         <v>45630</v>
       </c>
     </row>
@@ -10016,12 +10061,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10337,29 +10393,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10386,13 +10435,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
